--- a/comissoes_wilson_2025_26.xlsx
+++ b/comissoes_wilson_2025_26.xlsx
@@ -193,7 +193,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="42">
+  <cellXfs count="40">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
@@ -296,12 +296,6 @@
     </xf>
     <xf numFmtId="165" fontId="13" fillId="5" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="7" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="7" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="2" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center"/>
@@ -703,7 +697,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:R149"/>
+  <dimension ref="A1:R241"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="32" customWidth="1" min="1" max="1"/>
@@ -8397,577 +8391,6535 @@
       </c>
     </row>
     <row r="131" ht="16" customHeight="1">
-      <c r="A131" s="28" t="inlineStr">
-        <is>
-          <t>⚠  Dados de out/25 ainda não inseridos — preencher manualmente</t>
-        </is>
-      </c>
-    </row>
-    <row r="133" ht="22" customHeight="1">
-      <c r="A133" s="3" t="inlineStr">
+      <c r="A131" s="6" t="inlineStr">
+        <is>
+          <t>JULIO CESAR ALMEIDA DE OLIVEIRA</t>
+        </is>
+      </c>
+      <c r="B131" s="7" t="n">
+        <v>2089.08</v>
+      </c>
+      <c r="C131" s="8" t="inlineStr">
+        <is>
+          <t>TOKIO MARINE</t>
+        </is>
+      </c>
+      <c r="D131" s="8" t="inlineStr">
+        <is>
+          <t>I30</t>
+        </is>
+      </c>
+      <c r="E131" s="9" t="n">
+        <v>20</v>
+      </c>
+      <c r="F131" s="10" t="n">
+        <v>417.82</v>
+      </c>
+      <c r="G131" s="10" t="n">
+        <v>108.63</v>
+      </c>
+      <c r="H131" s="10" t="n">
+        <v>2.17</v>
+      </c>
+      <c r="I131" s="10" t="n">
+        <v>106.46</v>
+      </c>
+      <c r="J131" s="8" t="n">
+        <v>12</v>
+      </c>
+      <c r="K131" s="10" t="n">
+        <v>8.869999999999999</v>
+      </c>
+      <c r="L131" s="23" t="n">
+        <v>10</v>
+      </c>
+      <c r="M131" s="8" t="inlineStr">
+        <is>
+          <t>DE</t>
+        </is>
+      </c>
+      <c r="N131" s="12" t="n">
+        <v>12</v>
+      </c>
+      <c r="O131" s="10" t="n"/>
+      <c r="P131" s="13" t="inlineStr">
+        <is>
+          <t>Ativo</t>
+        </is>
+      </c>
+      <c r="Q131" s="13" t="inlineStr">
+        <is>
+          <t>Adimplente</t>
+        </is>
+      </c>
+      <c r="R131" s="14" t="inlineStr"/>
+    </row>
+    <row r="132" ht="16" customHeight="1">
+      <c r="A132" s="15" t="inlineStr">
+        <is>
+          <t>ROBSON NASCIMENTO SANTOS</t>
+        </is>
+      </c>
+      <c r="B132" s="16" t="n">
+        <v>3329.52</v>
+      </c>
+      <c r="C132" s="17" t="inlineStr">
+        <is>
+          <t>SUHAI</t>
+        </is>
+      </c>
+      <c r="D132" s="17" t="inlineStr">
+        <is>
+          <t>CITY</t>
+        </is>
+      </c>
+      <c r="E132" s="18" t="n">
+        <v>15</v>
+      </c>
+      <c r="F132" s="19" t="n">
+        <v>499.43</v>
+      </c>
+      <c r="G132" s="19" t="n">
+        <v>129.85</v>
+      </c>
+      <c r="H132" s="19" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="I132" s="19" t="n">
+        <v>127.25</v>
+      </c>
+      <c r="J132" s="17" t="n">
+        <v>12</v>
+      </c>
+      <c r="K132" s="19" t="n">
+        <v>10.6</v>
+      </c>
+      <c r="L132" s="24" t="n">
+        <v>11</v>
+      </c>
+      <c r="M132" s="17" t="inlineStr">
+        <is>
+          <t>DE</t>
+        </is>
+      </c>
+      <c r="N132" s="21" t="n">
+        <v>12</v>
+      </c>
+      <c r="O132" s="19" t="n"/>
+      <c r="P132" s="13" t="inlineStr">
+        <is>
+          <t>Ativo</t>
+        </is>
+      </c>
+      <c r="Q132" s="13" t="inlineStr">
+        <is>
+          <t>Adimplente</t>
+        </is>
+      </c>
+      <c r="R132" s="22" t="inlineStr"/>
+    </row>
+    <row r="133" ht="16" customHeight="1">
+      <c r="A133" s="6" t="inlineStr">
+        <is>
+          <t>FRANCISCO FERNANDES DE LIMA</t>
+        </is>
+      </c>
+      <c r="B133" s="7" t="n">
+        <v>1752.74</v>
+      </c>
+      <c r="C133" s="8" t="inlineStr">
+        <is>
+          <t>ALIRO</t>
+        </is>
+      </c>
+      <c r="D133" s="8" t="inlineStr">
+        <is>
+          <t>CRETA</t>
+        </is>
+      </c>
+      <c r="E133" s="9" t="n">
+        <v>20</v>
+      </c>
+      <c r="F133" s="10" t="n">
+        <v>350.55</v>
+      </c>
+      <c r="G133" s="10" t="n">
+        <v>91.14</v>
+      </c>
+      <c r="H133" s="10" t="n">
+        <v>1.82</v>
+      </c>
+      <c r="I133" s="10" t="n">
+        <v>89.31999999999999</v>
+      </c>
+      <c r="J133" s="8" t="n">
+        <v>12</v>
+      </c>
+      <c r="K133" s="10" t="n">
+        <v>7.44</v>
+      </c>
+      <c r="L133" s="23" t="n">
+        <v>9</v>
+      </c>
+      <c r="M133" s="8" t="inlineStr">
+        <is>
+          <t>DE</t>
+        </is>
+      </c>
+      <c r="N133" s="12" t="n">
+        <v>12</v>
+      </c>
+      <c r="O133" s="10" t="n"/>
+      <c r="P133" s="13" t="inlineStr">
+        <is>
+          <t>Ativo</t>
+        </is>
+      </c>
+      <c r="Q133" s="13" t="inlineStr">
+        <is>
+          <t>Adimplente</t>
+        </is>
+      </c>
+      <c r="R133" s="14" t="inlineStr"/>
+    </row>
+    <row r="134" ht="16" customHeight="1">
+      <c r="A134" s="15" t="inlineStr">
+        <is>
+          <t>RAFAEL SANTOS NASCIMENTO</t>
+        </is>
+      </c>
+      <c r="B134" s="16" t="n">
+        <v>3336.34</v>
+      </c>
+      <c r="C134" s="17" t="inlineStr">
+        <is>
+          <t>AZUL</t>
+        </is>
+      </c>
+      <c r="D134" s="17" t="inlineStr">
+        <is>
+          <t>CIVIC</t>
+        </is>
+      </c>
+      <c r="E134" s="18" t="n">
+        <v>20</v>
+      </c>
+      <c r="F134" s="19" t="n">
+        <v>667.27</v>
+      </c>
+      <c r="G134" s="19" t="n">
+        <v>173.49</v>
+      </c>
+      <c r="H134" s="19" t="n">
+        <v>3.47</v>
+      </c>
+      <c r="I134" s="19" t="n">
+        <v>170.02</v>
+      </c>
+      <c r="J134" s="17" t="n">
+        <v>10</v>
+      </c>
+      <c r="K134" s="19" t="n">
+        <v>17</v>
+      </c>
+      <c r="L134" s="24" t="n">
+        <v>9</v>
+      </c>
+      <c r="M134" s="17" t="inlineStr">
+        <is>
+          <t>DE</t>
+        </is>
+      </c>
+      <c r="N134" s="21" t="n">
+        <v>10</v>
+      </c>
+      <c r="O134" s="19" t="n"/>
+      <c r="P134" s="13" t="inlineStr">
+        <is>
+          <t>Ativo</t>
+        </is>
+      </c>
+      <c r="Q134" s="13" t="inlineStr">
+        <is>
+          <t>Adimplente</t>
+        </is>
+      </c>
+      <c r="R134" s="22" t="inlineStr"/>
+    </row>
+    <row r="135" ht="16" customHeight="1">
+      <c r="A135" s="6" t="inlineStr">
+        <is>
+          <t>ELIZABETH IZAGUIRRE GOMES</t>
+        </is>
+      </c>
+      <c r="B135" s="7" t="n">
+        <v>1029.05</v>
+      </c>
+      <c r="C135" s="8" t="inlineStr">
+        <is>
+          <t>HDI</t>
+        </is>
+      </c>
+      <c r="D135" s="8" t="inlineStr">
+        <is>
+          <t>PALIO</t>
+        </is>
+      </c>
+      <c r="E135" s="9" t="n">
+        <v>20</v>
+      </c>
+      <c r="F135" s="10" t="n">
+        <v>205.81</v>
+      </c>
+      <c r="G135" s="10" t="n">
+        <v>53.51</v>
+      </c>
+      <c r="H135" s="10" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="I135" s="10" t="n">
+        <v>52.44</v>
+      </c>
+      <c r="J135" s="8" t="n">
+        <v>10</v>
+      </c>
+      <c r="K135" s="10" t="n">
+        <v>5.24</v>
+      </c>
+      <c r="L135" s="23" t="n">
+        <v>9</v>
+      </c>
+      <c r="M135" s="8" t="inlineStr">
+        <is>
+          <t>DE</t>
+        </is>
+      </c>
+      <c r="N135" s="12" t="n">
+        <v>10</v>
+      </c>
+      <c r="O135" s="10" t="n"/>
+      <c r="P135" s="13" t="inlineStr">
+        <is>
+          <t>Ativo</t>
+        </is>
+      </c>
+      <c r="Q135" s="13" t="inlineStr">
+        <is>
+          <t>Adimplente</t>
+        </is>
+      </c>
+      <c r="R135" s="14" t="inlineStr"/>
+    </row>
+    <row r="136" ht="16" customHeight="1">
+      <c r="A136" s="15" t="inlineStr">
+        <is>
+          <t>FRANCISCO FERNANDES DE LIMA</t>
+        </is>
+      </c>
+      <c r="B136" s="16" t="n">
+        <v>1613.57</v>
+      </c>
+      <c r="C136" s="17" t="inlineStr">
+        <is>
+          <t>TOKIO MARINE</t>
+        </is>
+      </c>
+      <c r="D136" s="17" t="inlineStr">
+        <is>
+          <t>CITY</t>
+        </is>
+      </c>
+      <c r="E136" s="18" t="n">
+        <v>20</v>
+      </c>
+      <c r="F136" s="19" t="n">
+        <v>322.71</v>
+      </c>
+      <c r="G136" s="19" t="n">
+        <v>83.91</v>
+      </c>
+      <c r="H136" s="19" t="n">
+        <v>1.68</v>
+      </c>
+      <c r="I136" s="19" t="n">
+        <v>82.23</v>
+      </c>
+      <c r="J136" s="17" t="n">
+        <v>12</v>
+      </c>
+      <c r="K136" s="19" t="n">
+        <v>6.85</v>
+      </c>
+      <c r="L136" s="24" t="n">
+        <v>11</v>
+      </c>
+      <c r="M136" s="17" t="inlineStr">
+        <is>
+          <t>DE</t>
+        </is>
+      </c>
+      <c r="N136" s="21" t="n">
+        <v>12</v>
+      </c>
+      <c r="O136" s="19" t="n"/>
+      <c r="P136" s="13" t="inlineStr">
+        <is>
+          <t>Ativo</t>
+        </is>
+      </c>
+      <c r="Q136" s="13" t="inlineStr">
+        <is>
+          <t>Adimplente</t>
+        </is>
+      </c>
+      <c r="R136" s="22" t="inlineStr"/>
+    </row>
+    <row r="137" ht="16" customHeight="1">
+      <c r="A137" s="6" t="inlineStr">
+        <is>
+          <t>SOLANGE SILVA DE JESUS</t>
+        </is>
+      </c>
+      <c r="B137" s="7" t="n">
+        <v>1602.96</v>
+      </c>
+      <c r="C137" s="8" t="inlineStr">
+        <is>
+          <t>TOKIO MARINE</t>
+        </is>
+      </c>
+      <c r="D137" s="8" t="inlineStr">
+        <is>
+          <t>I30</t>
+        </is>
+      </c>
+      <c r="E137" s="9" t="n">
+        <v>20</v>
+      </c>
+      <c r="F137" s="10" t="n">
+        <v>320.59</v>
+      </c>
+      <c r="G137" s="10" t="n">
+        <v>83.34999999999999</v>
+      </c>
+      <c r="H137" s="10" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="I137" s="10" t="n">
+        <v>81.69</v>
+      </c>
+      <c r="J137" s="8" t="n">
+        <v>12</v>
+      </c>
+      <c r="K137" s="10" t="n">
+        <v>6.81</v>
+      </c>
+      <c r="L137" s="23" t="n">
+        <v>7</v>
+      </c>
+      <c r="M137" s="8" t="inlineStr">
+        <is>
+          <t>DE</t>
+        </is>
+      </c>
+      <c r="N137" s="12" t="n">
+        <v>12</v>
+      </c>
+      <c r="O137" s="10" t="n"/>
+      <c r="P137" s="13" t="inlineStr">
+        <is>
+          <t>Ativo</t>
+        </is>
+      </c>
+      <c r="Q137" s="13" t="inlineStr">
+        <is>
+          <t>Adimplente</t>
+        </is>
+      </c>
+      <c r="R137" s="14" t="inlineStr"/>
+    </row>
+    <row r="138" ht="16" customHeight="1">
+      <c r="A138" s="15" t="inlineStr">
+        <is>
+          <t>ROSANGELA DE JESUS MELO</t>
+        </is>
+      </c>
+      <c r="B138" s="16" t="n">
+        <v>1454.42</v>
+      </c>
+      <c r="C138" s="17" t="inlineStr">
+        <is>
+          <t>SUHAI</t>
+        </is>
+      </c>
+      <c r="D138" s="17" t="inlineStr">
+        <is>
+          <t>IDEA</t>
+        </is>
+      </c>
+      <c r="E138" s="18" t="n">
+        <v>25</v>
+      </c>
+      <c r="F138" s="19" t="n">
+        <v>363.61</v>
+      </c>
+      <c r="G138" s="19" t="n">
+        <v>94.54000000000001</v>
+      </c>
+      <c r="H138" s="19" t="n">
+        <v>1.89</v>
+      </c>
+      <c r="I138" s="19" t="n">
+        <v>92.65000000000001</v>
+      </c>
+      <c r="J138" s="17" t="n">
+        <v>1</v>
+      </c>
+      <c r="K138" s="19" t="n">
+        <v>92.65000000000001</v>
+      </c>
+      <c r="L138" s="24" t="n">
+        <v>5</v>
+      </c>
+      <c r="M138" s="17" t="inlineStr">
+        <is>
+          <t>DE</t>
+        </is>
+      </c>
+      <c r="N138" s="21" t="n">
+        <v>1</v>
+      </c>
+      <c r="O138" s="19" t="n"/>
+      <c r="P138" s="13" t="inlineStr">
+        <is>
+          <t>Ativo</t>
+        </is>
+      </c>
+      <c r="Q138" s="13" t="inlineStr">
+        <is>
+          <t>Adimplente</t>
+        </is>
+      </c>
+      <c r="R138" s="22" t="inlineStr"/>
+    </row>
+    <row r="139" ht="16" customHeight="1">
+      <c r="A139" s="6" t="inlineStr">
+        <is>
+          <t>ANTONIO CARLOS DOS SANTOS</t>
+        </is>
+      </c>
+      <c r="B139" s="7" t="n">
+        <v>2201.31</v>
+      </c>
+      <c r="C139" s="8" t="inlineStr">
+        <is>
+          <t>PORTO</t>
+        </is>
+      </c>
+      <c r="D139" s="8" t="inlineStr">
+        <is>
+          <t>TUCSON</t>
+        </is>
+      </c>
+      <c r="E139" s="9" t="n">
+        <v>18</v>
+      </c>
+      <c r="F139" s="10" t="n">
+        <v>396.24</v>
+      </c>
+      <c r="G139" s="10" t="n">
+        <v>103.02</v>
+      </c>
+      <c r="H139" s="10" t="n">
+        <v>2.06</v>
+      </c>
+      <c r="I139" s="10" t="n">
+        <v>100.96</v>
+      </c>
+      <c r="J139" s="8" t="n">
+        <v>10</v>
+      </c>
+      <c r="K139" s="10" t="n">
+        <v>10.1</v>
+      </c>
+      <c r="L139" s="23" t="n">
+        <v>5</v>
+      </c>
+      <c r="M139" s="8" t="inlineStr">
+        <is>
+          <t>DE</t>
+        </is>
+      </c>
+      <c r="N139" s="12" t="n">
+        <v>10</v>
+      </c>
+      <c r="O139" s="10" t="n"/>
+      <c r="P139" s="13" t="inlineStr">
+        <is>
+          <t>Ativo</t>
+        </is>
+      </c>
+      <c r="Q139" s="13" t="inlineStr">
+        <is>
+          <t>Adimplente</t>
+        </is>
+      </c>
+      <c r="R139" s="14" t="inlineStr"/>
+    </row>
+    <row r="140" ht="16" customHeight="1">
+      <c r="A140" s="15" t="inlineStr">
+        <is>
+          <t>OTAVIANO DE JESUS</t>
+        </is>
+      </c>
+      <c r="B140" s="16" t="n">
+        <v>1854.88</v>
+      </c>
+      <c r="C140" s="17" t="inlineStr">
+        <is>
+          <t>PORTO</t>
+        </is>
+      </c>
+      <c r="D140" s="17" t="inlineStr">
+        <is>
+          <t>CORSA</t>
+        </is>
+      </c>
+      <c r="E140" s="18" t="n">
+        <v>18</v>
+      </c>
+      <c r="F140" s="19" t="n">
+        <v>333.88</v>
+      </c>
+      <c r="G140" s="19" t="n">
+        <v>86.81</v>
+      </c>
+      <c r="H140" s="19" t="n">
+        <v>1.74</v>
+      </c>
+      <c r="I140" s="19" t="n">
+        <v>85.06999999999999</v>
+      </c>
+      <c r="J140" s="17" t="n">
+        <v>10</v>
+      </c>
+      <c r="K140" s="19" t="n">
+        <v>8.51</v>
+      </c>
+      <c r="L140" s="24" t="n">
+        <v>5</v>
+      </c>
+      <c r="M140" s="17" t="inlineStr">
+        <is>
+          <t>DE</t>
+        </is>
+      </c>
+      <c r="N140" s="21" t="n">
+        <v>10</v>
+      </c>
+      <c r="O140" s="19" t="n"/>
+      <c r="P140" s="13" t="inlineStr">
+        <is>
+          <t>Ativo</t>
+        </is>
+      </c>
+      <c r="Q140" s="13" t="inlineStr">
+        <is>
+          <t>Adimplente</t>
+        </is>
+      </c>
+      <c r="R140" s="22" t="inlineStr"/>
+    </row>
+    <row r="141" ht="16" customHeight="1">
+      <c r="A141" s="6" t="inlineStr">
+        <is>
+          <t>LEONARDO VAZ DE FREITAS</t>
+        </is>
+      </c>
+      <c r="B141" s="7" t="n">
+        <v>1689.84</v>
+      </c>
+      <c r="C141" s="8" t="inlineStr">
+        <is>
+          <t>SUHAI</t>
+        </is>
+      </c>
+      <c r="D141" s="8" t="inlineStr">
+        <is>
+          <t>TUCSON</t>
+        </is>
+      </c>
+      <c r="E141" s="9" t="n">
+        <v>25</v>
+      </c>
+      <c r="F141" s="10" t="n">
+        <v>422.46</v>
+      </c>
+      <c r="G141" s="10" t="n">
+        <v>109.84</v>
+      </c>
+      <c r="H141" s="10" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="I141" s="10" t="n">
+        <v>107.64</v>
+      </c>
+      <c r="J141" s="8" t="n">
+        <v>12</v>
+      </c>
+      <c r="K141" s="10" t="n">
+        <v>8.970000000000001</v>
+      </c>
+      <c r="L141" s="23" t="n">
+        <v>5</v>
+      </c>
+      <c r="M141" s="8" t="inlineStr">
+        <is>
+          <t>DE</t>
+        </is>
+      </c>
+      <c r="N141" s="12" t="n">
+        <v>12</v>
+      </c>
+      <c r="O141" s="10" t="n"/>
+      <c r="P141" s="13" t="inlineStr">
+        <is>
+          <t>Ativo</t>
+        </is>
+      </c>
+      <c r="Q141" s="13" t="inlineStr">
+        <is>
+          <t>Adimplente</t>
+        </is>
+      </c>
+      <c r="R141" s="14" t="inlineStr"/>
+    </row>
+    <row r="142" ht="16" customHeight="1">
+      <c r="A142" s="15" t="inlineStr">
+        <is>
+          <t>VALDISLEI XAVIER DO NASCIMENTO</t>
+        </is>
+      </c>
+      <c r="B142" s="16" t="n">
+        <v>4204.31</v>
+      </c>
+      <c r="C142" s="17" t="inlineStr">
+        <is>
+          <t>BRADESCO</t>
+        </is>
+      </c>
+      <c r="D142" s="17" t="inlineStr">
+        <is>
+          <t>COROLLA</t>
+        </is>
+      </c>
+      <c r="E142" s="18" t="n">
+        <v>20</v>
+      </c>
+      <c r="F142" s="19" t="n">
+        <v>840.86</v>
+      </c>
+      <c r="G142" s="19" t="n">
+        <v>218.62</v>
+      </c>
+      <c r="H142" s="19" t="n">
+        <v>4.37</v>
+      </c>
+      <c r="I142" s="19" t="n">
+        <v>214.25</v>
+      </c>
+      <c r="J142" s="17" t="n">
+        <v>10</v>
+      </c>
+      <c r="K142" s="19" t="n">
+        <v>21.43</v>
+      </c>
+      <c r="L142" s="24" t="n">
+        <v>4</v>
+      </c>
+      <c r="M142" s="17" t="inlineStr">
+        <is>
+          <t>DE</t>
+        </is>
+      </c>
+      <c r="N142" s="21" t="n">
+        <v>10</v>
+      </c>
+      <c r="O142" s="19" t="n"/>
+      <c r="P142" s="13" t="inlineStr">
+        <is>
+          <t>Ativo</t>
+        </is>
+      </c>
+      <c r="Q142" s="13" t="inlineStr">
+        <is>
+          <t>Adimplente</t>
+        </is>
+      </c>
+      <c r="R142" s="22" t="inlineStr"/>
+    </row>
+    <row r="143" ht="16" customHeight="1">
+      <c r="A143" s="6" t="inlineStr">
+        <is>
+          <t>DERANILDA PEREIRA COELHO</t>
+        </is>
+      </c>
+      <c r="B143" s="7" t="n">
+        <v>1553.27</v>
+      </c>
+      <c r="C143" s="8" t="inlineStr">
+        <is>
+          <t>SUHAI</t>
+        </is>
+      </c>
+      <c r="D143" s="8" t="inlineStr">
+        <is>
+          <t>ZARIFA</t>
+        </is>
+      </c>
+      <c r="E143" s="9" t="n">
+        <v>20</v>
+      </c>
+      <c r="F143" s="10" t="n">
+        <v>310.65</v>
+      </c>
+      <c r="G143" s="10" t="n">
+        <v>80.77</v>
+      </c>
+      <c r="H143" s="10" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="I143" s="10" t="n">
+        <v>79.15000000000001</v>
+      </c>
+      <c r="J143" s="8" t="n">
+        <v>5</v>
+      </c>
+      <c r="K143" s="10" t="n">
+        <v>15.83</v>
+      </c>
+      <c r="L143" s="23" t="n">
+        <v>4</v>
+      </c>
+      <c r="M143" s="8" t="inlineStr">
+        <is>
+          <t>DE</t>
+        </is>
+      </c>
+      <c r="N143" s="12" t="n">
+        <v>5</v>
+      </c>
+      <c r="O143" s="10" t="n"/>
+      <c r="P143" s="13" t="inlineStr">
+        <is>
+          <t>Ativo</t>
+        </is>
+      </c>
+      <c r="Q143" s="13" t="inlineStr">
+        <is>
+          <t>Adimplente</t>
+        </is>
+      </c>
+      <c r="R143" s="14" t="inlineStr"/>
+    </row>
+    <row r="144" ht="16" customHeight="1">
+      <c r="A144" s="15" t="inlineStr">
+        <is>
+          <t>IVO REIS DO NASCIMENTO</t>
+        </is>
+      </c>
+      <c r="B144" s="16" t="n">
+        <v>1199.51</v>
+      </c>
+      <c r="C144" s="17" t="inlineStr">
+        <is>
+          <t>AZUL</t>
+        </is>
+      </c>
+      <c r="D144" s="17" t="inlineStr">
+        <is>
+          <t>CITY SEDAN</t>
+        </is>
+      </c>
+      <c r="E144" s="18" t="n">
+        <v>20</v>
+      </c>
+      <c r="F144" s="19" t="n">
+        <v>239.9</v>
+      </c>
+      <c r="G144" s="19" t="n">
+        <v>62.37</v>
+      </c>
+      <c r="H144" s="19" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="I144" s="19" t="n">
+        <v>61.13</v>
+      </c>
+      <c r="J144" s="17" t="n">
+        <v>1</v>
+      </c>
+      <c r="K144" s="19" t="n">
+        <v>61.13</v>
+      </c>
+      <c r="L144" s="24" t="n">
+        <v>4</v>
+      </c>
+      <c r="M144" s="17" t="inlineStr">
+        <is>
+          <t>DE</t>
+        </is>
+      </c>
+      <c r="N144" s="21" t="n">
+        <v>1</v>
+      </c>
+      <c r="O144" s="19" t="n"/>
+      <c r="P144" s="13" t="inlineStr">
+        <is>
+          <t>Ativo</t>
+        </is>
+      </c>
+      <c r="Q144" s="13" t="inlineStr">
+        <is>
+          <t>Adimplente</t>
+        </is>
+      </c>
+      <c r="R144" s="22" t="inlineStr"/>
+    </row>
+    <row r="145" ht="16" customHeight="1">
+      <c r="A145" s="6" t="inlineStr">
+        <is>
+          <t>ANDREA NASCIMENTO SANTANA MARTIENA</t>
+        </is>
+      </c>
+      <c r="B145" s="7" t="n">
+        <v>1986.95</v>
+      </c>
+      <c r="C145" s="8" t="inlineStr">
+        <is>
+          <t>TOKIO MARINE</t>
+        </is>
+      </c>
+      <c r="D145" s="8" t="inlineStr">
+        <is>
+          <t>CRETA</t>
+        </is>
+      </c>
+      <c r="E145" s="9" t="n">
+        <v>20</v>
+      </c>
+      <c r="F145" s="10" t="n">
+        <v>397.39</v>
+      </c>
+      <c r="G145" s="10" t="n">
+        <v>103.32</v>
+      </c>
+      <c r="H145" s="10" t="n">
+        <v>2.07</v>
+      </c>
+      <c r="I145" s="10" t="n">
+        <v>101.25</v>
+      </c>
+      <c r="J145" s="8" t="n">
+        <v>12</v>
+      </c>
+      <c r="K145" s="10" t="n">
+        <v>8.44</v>
+      </c>
+      <c r="L145" s="23" t="n">
+        <v>4</v>
+      </c>
+      <c r="M145" s="8" t="inlineStr">
+        <is>
+          <t>DE</t>
+        </is>
+      </c>
+      <c r="N145" s="12" t="n">
+        <v>12</v>
+      </c>
+      <c r="O145" s="10" t="n"/>
+      <c r="P145" s="13" t="inlineStr">
+        <is>
+          <t>Ativo</t>
+        </is>
+      </c>
+      <c r="Q145" s="13" t="inlineStr">
+        <is>
+          <t>Adimplente</t>
+        </is>
+      </c>
+      <c r="R145" s="14" t="inlineStr"/>
+    </row>
+    <row r="146" ht="16" customHeight="1">
+      <c r="A146" s="15" t="inlineStr">
+        <is>
+          <t>CAIO CESAR DOS SANTOS</t>
+        </is>
+      </c>
+      <c r="B146" s="16" t="n">
+        <v>3310.55</v>
+      </c>
+      <c r="C146" s="17" t="inlineStr">
+        <is>
+          <t>SUHAI</t>
+        </is>
+      </c>
+      <c r="D146" s="17" t="inlineStr">
+        <is>
+          <t>SIENA</t>
+        </is>
+      </c>
+      <c r="E146" s="18" t="n">
+        <v>20</v>
+      </c>
+      <c r="F146" s="19" t="n">
+        <v>662.11</v>
+      </c>
+      <c r="G146" s="19" t="n">
+        <v>172.15</v>
+      </c>
+      <c r="H146" s="19" t="n">
+        <v>3.44</v>
+      </c>
+      <c r="I146" s="19" t="n">
+        <v>168.71</v>
+      </c>
+      <c r="J146" s="17" t="n">
+        <v>12</v>
+      </c>
+      <c r="K146" s="19" t="n">
+        <v>14.06</v>
+      </c>
+      <c r="L146" s="24" t="n">
+        <v>3</v>
+      </c>
+      <c r="M146" s="17" t="inlineStr">
+        <is>
+          <t>DE</t>
+        </is>
+      </c>
+      <c r="N146" s="21" t="n">
+        <v>12</v>
+      </c>
+      <c r="O146" s="19" t="n"/>
+      <c r="P146" s="13" t="inlineStr">
+        <is>
+          <t>Ativo</t>
+        </is>
+      </c>
+      <c r="Q146" s="13" t="inlineStr">
+        <is>
+          <t>Adimplente</t>
+        </is>
+      </c>
+      <c r="R146" s="22" t="inlineStr"/>
+    </row>
+    <row r="147" ht="16" customHeight="1">
+      <c r="A147" s="6" t="inlineStr">
+        <is>
+          <t>IVO REIS DO NASCIMENTO</t>
+        </is>
+      </c>
+      <c r="B147" s="7" t="n">
+        <v>2141.74</v>
+      </c>
+      <c r="C147" s="8" t="inlineStr">
+        <is>
+          <t>MITSUI</t>
+        </is>
+      </c>
+      <c r="D147" s="8" t="inlineStr">
+        <is>
+          <t>FOX</t>
+        </is>
+      </c>
+      <c r="E147" s="9" t="n">
+        <v>20</v>
+      </c>
+      <c r="F147" s="10" t="n">
+        <v>428.35</v>
+      </c>
+      <c r="G147" s="10" t="n">
+        <v>111.37</v>
+      </c>
+      <c r="H147" s="10" t="n">
+        <v>2.23</v>
+      </c>
+      <c r="I147" s="10" t="n">
+        <v>109.14</v>
+      </c>
+      <c r="J147" s="8" t="n">
+        <v>10</v>
+      </c>
+      <c r="K147" s="10" t="n">
+        <v>10.91</v>
+      </c>
+      <c r="L147" s="23" t="n">
+        <v>3</v>
+      </c>
+      <c r="M147" s="8" t="inlineStr">
+        <is>
+          <t>DE</t>
+        </is>
+      </c>
+      <c r="N147" s="12" t="n">
+        <v>10</v>
+      </c>
+      <c r="O147" s="10" t="n"/>
+      <c r="P147" s="13" t="inlineStr">
+        <is>
+          <t>Ativo</t>
+        </is>
+      </c>
+      <c r="Q147" s="13" t="inlineStr">
+        <is>
+          <t>Adimplente</t>
+        </is>
+      </c>
+      <c r="R147" s="14" t="inlineStr"/>
+    </row>
+    <row r="148" ht="16" customHeight="1">
+      <c r="A148" s="15" t="inlineStr">
+        <is>
+          <t>FRANCISCO FERNANDES DE LIMA</t>
+        </is>
+      </c>
+      <c r="B148" s="16" t="n">
+        <v>326.96</v>
+      </c>
+      <c r="C148" s="17" t="inlineStr">
+        <is>
+          <t>ALIRO</t>
+        </is>
+      </c>
+      <c r="D148" s="17" t="inlineStr">
+        <is>
+          <t>TRACKER</t>
+        </is>
+      </c>
+      <c r="E148" s="18" t="n">
+        <v>20</v>
+      </c>
+      <c r="F148" s="19" t="n">
+        <v>65.39</v>
+      </c>
+      <c r="G148" s="19" t="n">
+        <v>17</v>
+      </c>
+      <c r="H148" s="19" t="n">
+        <v>0.34</v>
+      </c>
+      <c r="I148" s="19" t="n">
+        <v>16.66</v>
+      </c>
+      <c r="J148" s="17" t="n">
+        <v>3</v>
+      </c>
+      <c r="K148" s="19" t="n">
+        <v>5.55</v>
+      </c>
+      <c r="L148" s="20" t="n">
+        <v>3</v>
+      </c>
+      <c r="M148" s="17" t="inlineStr">
+        <is>
+          <t>DE</t>
+        </is>
+      </c>
+      <c r="N148" s="21" t="n">
+        <v>3</v>
+      </c>
+      <c r="O148" s="19" t="n"/>
+      <c r="P148" s="13" t="inlineStr">
+        <is>
+          <t>Ativo</t>
+        </is>
+      </c>
+      <c r="Q148" s="13" t="inlineStr">
+        <is>
+          <t>Adimplente</t>
+        </is>
+      </c>
+      <c r="R148" s="22" t="inlineStr"/>
+    </row>
+    <row r="149" ht="16" customHeight="1">
+      <c r="A149" s="6" t="inlineStr">
+        <is>
+          <t>LEIDE DAYANE DE SOUZA</t>
+        </is>
+      </c>
+      <c r="B149" s="7" t="n">
+        <v>1642.98</v>
+      </c>
+      <c r="C149" s="8" t="inlineStr">
+        <is>
+          <t>ALIRO</t>
+        </is>
+      </c>
+      <c r="D149" s="8" t="inlineStr">
+        <is>
+          <t>ECOSPORT</t>
+        </is>
+      </c>
+      <c r="E149" s="9" t="n">
+        <v>20</v>
+      </c>
+      <c r="F149" s="10" t="n">
+        <v>328.6</v>
+      </c>
+      <c r="G149" s="10" t="n">
+        <v>85.43000000000001</v>
+      </c>
+      <c r="H149" s="10" t="n">
+        <v>1.71</v>
+      </c>
+      <c r="I149" s="10" t="n">
+        <v>83.73</v>
+      </c>
+      <c r="J149" s="8" t="n">
+        <v>10</v>
+      </c>
+      <c r="K149" s="10" t="n">
+        <v>8.369999999999999</v>
+      </c>
+      <c r="L149" s="23" t="n">
+        <v>3</v>
+      </c>
+      <c r="M149" s="8" t="inlineStr">
+        <is>
+          <t>DE</t>
+        </is>
+      </c>
+      <c r="N149" s="12" t="n">
+        <v>10</v>
+      </c>
+      <c r="O149" s="10" t="n"/>
+      <c r="P149" s="13" t="inlineStr">
+        <is>
+          <t>Ativo</t>
+        </is>
+      </c>
+      <c r="Q149" s="13" t="inlineStr">
+        <is>
+          <t>Adimplente</t>
+        </is>
+      </c>
+      <c r="R149" s="14" t="inlineStr"/>
+    </row>
+    <row r="150" ht="18" customHeight="1">
+      <c r="A150" s="25" t="inlineStr">
+        <is>
+          <t>TOTAL  OUT/25</t>
+        </is>
+      </c>
+      <c r="K150" s="26" t="n">
+        <v>328.76</v>
+      </c>
+      <c r="L150" s="27" t="n"/>
+      <c r="M150" s="27" t="n"/>
+      <c r="N150" s="27" t="n"/>
+      <c r="O150" s="27" t="n"/>
+      <c r="P150" s="27" t="n"/>
+      <c r="Q150" s="27" t="n"/>
+      <c r="R150" s="27" t="n"/>
+    </row>
+    <row r="152" ht="22" customHeight="1">
+      <c r="A152" s="3" t="inlineStr">
         <is>
           <t>nov/25</t>
         </is>
       </c>
-      <c r="B133" s="4" t="inlineStr">
+      <c r="B152" s="4" t="inlineStr">
         <is>
           <t>PRÊMIO LÍQ</t>
         </is>
       </c>
-      <c r="C133" s="4" t="inlineStr">
+      <c r="C152" s="4" t="inlineStr">
         <is>
           <t>SEGURADORA</t>
         </is>
       </c>
-      <c r="D133" s="4" t="inlineStr">
+      <c r="D152" s="4" t="inlineStr">
         <is>
           <t>ITEM</t>
         </is>
       </c>
-      <c r="E133" s="4" t="inlineStr">
+      <c r="E152" s="4" t="inlineStr">
         <is>
           <t>COM%</t>
         </is>
       </c>
-      <c r="F133" s="4" t="inlineStr">
+      <c r="F152" s="4" t="inlineStr">
         <is>
           <t>COMISSÃO</t>
         </is>
       </c>
-      <c r="G133" s="4" t="inlineStr">
+      <c r="G152" s="4" t="inlineStr">
         <is>
           <t>26%</t>
         </is>
       </c>
-      <c r="H133" s="4" t="inlineStr">
+      <c r="H152" s="4" t="inlineStr">
         <is>
           <t>2% DA</t>
         </is>
       </c>
-      <c r="I133" s="4" t="inlineStr">
+      <c r="I152" s="4" t="inlineStr">
         <is>
           <t>RECEBIDO</t>
         </is>
       </c>
-      <c r="J133" s="4" t="inlineStr">
+      <c r="J152" s="4" t="inlineStr">
         <is>
           <t>VEZES</t>
         </is>
       </c>
-      <c r="K133" s="4" t="inlineStr">
+      <c r="K152" s="4" t="inlineStr">
         <is>
           <t>RECEBER</t>
         </is>
       </c>
-      <c r="L133" s="5" t="inlineStr"/>
-      <c r="M133" s="4" t="inlineStr">
-        <is>
-          <t>DE</t>
-        </is>
-      </c>
-      <c r="N133" s="5" t="inlineStr"/>
-      <c r="O133" s="4" t="inlineStr">
+      <c r="L152" s="5" t="inlineStr"/>
+      <c r="M152" s="4" t="inlineStr">
+        <is>
+          <t>DE</t>
+        </is>
+      </c>
+      <c r="N152" s="5" t="inlineStr"/>
+      <c r="O152" s="4" t="inlineStr">
         <is>
           <t>AJUSTE</t>
         </is>
       </c>
-      <c r="P133" s="4" t="inlineStr">
+      <c r="P152" s="4" t="inlineStr">
         <is>
           <t>STATUS</t>
         </is>
       </c>
-      <c r="Q133" s="4" t="inlineStr">
+      <c r="Q152" s="4" t="inlineStr">
         <is>
           <t>ADIMPLÊNCIA</t>
         </is>
       </c>
-      <c r="R133" s="4" t="inlineStr">
+      <c r="R152" s="4" t="inlineStr">
         <is>
           <t>OBS</t>
         </is>
       </c>
     </row>
-    <row r="134" ht="16" customHeight="1">
-      <c r="A134" s="28" t="inlineStr">
-        <is>
-          <t>⚠  Dados de nov/25 ainda não inseridos — preencher manualmente</t>
-        </is>
-      </c>
-    </row>
-    <row r="136" ht="22" customHeight="1">
-      <c r="A136" s="3" t="inlineStr">
+    <row r="153" ht="16" customHeight="1">
+      <c r="A153" s="6" t="inlineStr">
+        <is>
+          <t>JULIO CESAR ALMEIDA DE OLIVEIRA</t>
+        </is>
+      </c>
+      <c r="B153" s="7" t="n">
+        <v>2089.08</v>
+      </c>
+      <c r="C153" s="8" t="inlineStr">
+        <is>
+          <t>TOKIO MARINE</t>
+        </is>
+      </c>
+      <c r="D153" s="8" t="inlineStr">
+        <is>
+          <t>I30</t>
+        </is>
+      </c>
+      <c r="E153" s="9" t="n">
+        <v>20</v>
+      </c>
+      <c r="F153" s="10" t="n">
+        <v>417.82</v>
+      </c>
+      <c r="G153" s="10" t="n">
+        <v>108.63</v>
+      </c>
+      <c r="H153" s="10" t="n">
+        <v>2.17</v>
+      </c>
+      <c r="I153" s="10" t="n">
+        <v>106.46</v>
+      </c>
+      <c r="J153" s="8" t="n">
+        <v>12</v>
+      </c>
+      <c r="K153" s="10" t="n">
+        <v>8.869999999999999</v>
+      </c>
+      <c r="L153" s="23" t="n">
+        <v>11</v>
+      </c>
+      <c r="M153" s="8" t="inlineStr">
+        <is>
+          <t>DE</t>
+        </is>
+      </c>
+      <c r="N153" s="12" t="n">
+        <v>12</v>
+      </c>
+      <c r="O153" s="10" t="n"/>
+      <c r="P153" s="13" t="inlineStr">
+        <is>
+          <t>Ativo</t>
+        </is>
+      </c>
+      <c r="Q153" s="13" t="inlineStr">
+        <is>
+          <t>Adimplente</t>
+        </is>
+      </c>
+      <c r="R153" s="14" t="inlineStr"/>
+    </row>
+    <row r="154" ht="16" customHeight="1">
+      <c r="A154" s="15" t="inlineStr">
+        <is>
+          <t>ROBSON NASCIMENTO SANTOS</t>
+        </is>
+      </c>
+      <c r="B154" s="16" t="n">
+        <v>3329.52</v>
+      </c>
+      <c r="C154" s="17" t="inlineStr">
+        <is>
+          <t>SUHAI</t>
+        </is>
+      </c>
+      <c r="D154" s="17" t="inlineStr">
+        <is>
+          <t>CITY</t>
+        </is>
+      </c>
+      <c r="E154" s="18" t="n">
+        <v>15</v>
+      </c>
+      <c r="F154" s="19" t="n">
+        <v>499.43</v>
+      </c>
+      <c r="G154" s="19" t="n">
+        <v>129.85</v>
+      </c>
+      <c r="H154" s="19" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="I154" s="19" t="n">
+        <v>127.25</v>
+      </c>
+      <c r="J154" s="17" t="n">
+        <v>12</v>
+      </c>
+      <c r="K154" s="19" t="n">
+        <v>10.6</v>
+      </c>
+      <c r="L154" s="20" t="n">
+        <v>12</v>
+      </c>
+      <c r="M154" s="17" t="inlineStr">
+        <is>
+          <t>DE</t>
+        </is>
+      </c>
+      <c r="N154" s="21" t="n">
+        <v>12</v>
+      </c>
+      <c r="O154" s="19" t="n"/>
+      <c r="P154" s="13" t="inlineStr">
+        <is>
+          <t>Ativo</t>
+        </is>
+      </c>
+      <c r="Q154" s="13" t="inlineStr">
+        <is>
+          <t>Adimplente</t>
+        </is>
+      </c>
+      <c r="R154" s="22" t="inlineStr"/>
+    </row>
+    <row r="155" ht="16" customHeight="1">
+      <c r="A155" s="6" t="inlineStr">
+        <is>
+          <t>FRANCISCO FERNANDES DE LIMA</t>
+        </is>
+      </c>
+      <c r="B155" s="7" t="n">
+        <v>1752.74</v>
+      </c>
+      <c r="C155" s="8" t="inlineStr">
+        <is>
+          <t>ALIRO</t>
+        </is>
+      </c>
+      <c r="D155" s="8" t="inlineStr">
+        <is>
+          <t>CRETA</t>
+        </is>
+      </c>
+      <c r="E155" s="9" t="n">
+        <v>20</v>
+      </c>
+      <c r="F155" s="10" t="n">
+        <v>350.55</v>
+      </c>
+      <c r="G155" s="10" t="n">
+        <v>91.14</v>
+      </c>
+      <c r="H155" s="10" t="n">
+        <v>1.82</v>
+      </c>
+      <c r="I155" s="10" t="n">
+        <v>89.31999999999999</v>
+      </c>
+      <c r="J155" s="8" t="n">
+        <v>12</v>
+      </c>
+      <c r="K155" s="10" t="n">
+        <v>7.44</v>
+      </c>
+      <c r="L155" s="23" t="n">
+        <v>10</v>
+      </c>
+      <c r="M155" s="8" t="inlineStr">
+        <is>
+          <t>DE</t>
+        </is>
+      </c>
+      <c r="N155" s="12" t="n">
+        <v>12</v>
+      </c>
+      <c r="O155" s="10" t="n"/>
+      <c r="P155" s="13" t="inlineStr">
+        <is>
+          <t>Ativo</t>
+        </is>
+      </c>
+      <c r="Q155" s="13" t="inlineStr">
+        <is>
+          <t>Adimplente</t>
+        </is>
+      </c>
+      <c r="R155" s="14" t="inlineStr"/>
+    </row>
+    <row r="156" ht="16" customHeight="1">
+      <c r="A156" s="15" t="inlineStr">
+        <is>
+          <t>RAFAEL SANTOS NASCIMENTO</t>
+        </is>
+      </c>
+      <c r="B156" s="16" t="n">
+        <v>3336.34</v>
+      </c>
+      <c r="C156" s="17" t="inlineStr">
+        <is>
+          <t>AZUL</t>
+        </is>
+      </c>
+      <c r="D156" s="17" t="inlineStr">
+        <is>
+          <t>CIVIC</t>
+        </is>
+      </c>
+      <c r="E156" s="18" t="n">
+        <v>20</v>
+      </c>
+      <c r="F156" s="19" t="n">
+        <v>667.27</v>
+      </c>
+      <c r="G156" s="19" t="n">
+        <v>173.49</v>
+      </c>
+      <c r="H156" s="19" t="n">
+        <v>3.47</v>
+      </c>
+      <c r="I156" s="19" t="n">
+        <v>170.02</v>
+      </c>
+      <c r="J156" s="17" t="n">
+        <v>10</v>
+      </c>
+      <c r="K156" s="19" t="n">
+        <v>17</v>
+      </c>
+      <c r="L156" s="20" t="n">
+        <v>10</v>
+      </c>
+      <c r="M156" s="17" t="inlineStr">
+        <is>
+          <t>DE</t>
+        </is>
+      </c>
+      <c r="N156" s="21" t="n">
+        <v>10</v>
+      </c>
+      <c r="O156" s="19" t="n"/>
+      <c r="P156" s="13" t="inlineStr">
+        <is>
+          <t>Ativo</t>
+        </is>
+      </c>
+      <c r="Q156" s="13" t="inlineStr">
+        <is>
+          <t>Adimplente</t>
+        </is>
+      </c>
+      <c r="R156" s="22" t="inlineStr"/>
+    </row>
+    <row r="157" ht="16" customHeight="1">
+      <c r="A157" s="6" t="inlineStr">
+        <is>
+          <t>ELIZABETH IZAGUIRRE GOMES</t>
+        </is>
+      </c>
+      <c r="B157" s="7" t="n">
+        <v>1029.05</v>
+      </c>
+      <c r="C157" s="8" t="inlineStr">
+        <is>
+          <t>HDI</t>
+        </is>
+      </c>
+      <c r="D157" s="8" t="inlineStr">
+        <is>
+          <t>PALIO</t>
+        </is>
+      </c>
+      <c r="E157" s="9" t="n">
+        <v>20</v>
+      </c>
+      <c r="F157" s="10" t="n">
+        <v>205.81</v>
+      </c>
+      <c r="G157" s="10" t="n">
+        <v>53.51</v>
+      </c>
+      <c r="H157" s="10" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="I157" s="10" t="n">
+        <v>52.44</v>
+      </c>
+      <c r="J157" s="8" t="n">
+        <v>10</v>
+      </c>
+      <c r="K157" s="10" t="n">
+        <v>5.24</v>
+      </c>
+      <c r="L157" s="11" t="n">
+        <v>10</v>
+      </c>
+      <c r="M157" s="8" t="inlineStr">
+        <is>
+          <t>DE</t>
+        </is>
+      </c>
+      <c r="N157" s="12" t="n">
+        <v>10</v>
+      </c>
+      <c r="O157" s="10" t="n"/>
+      <c r="P157" s="13" t="inlineStr">
+        <is>
+          <t>Ativo</t>
+        </is>
+      </c>
+      <c r="Q157" s="13" t="inlineStr">
+        <is>
+          <t>Adimplente</t>
+        </is>
+      </c>
+      <c r="R157" s="14" t="inlineStr"/>
+    </row>
+    <row r="158" ht="16" customHeight="1">
+      <c r="A158" s="15" t="inlineStr">
+        <is>
+          <t>FRANCISCO FERNANDES DE LIMA</t>
+        </is>
+      </c>
+      <c r="B158" s="16" t="n">
+        <v>1613.57</v>
+      </c>
+      <c r="C158" s="17" t="inlineStr">
+        <is>
+          <t>TOKIO MARINE</t>
+        </is>
+      </c>
+      <c r="D158" s="17" t="inlineStr">
+        <is>
+          <t>CITY</t>
+        </is>
+      </c>
+      <c r="E158" s="18" t="n">
+        <v>20</v>
+      </c>
+      <c r="F158" s="19" t="n">
+        <v>322.71</v>
+      </c>
+      <c r="G158" s="19" t="n">
+        <v>83.91</v>
+      </c>
+      <c r="H158" s="19" t="n">
+        <v>1.68</v>
+      </c>
+      <c r="I158" s="19" t="n">
+        <v>82.23</v>
+      </c>
+      <c r="J158" s="17" t="n">
+        <v>12</v>
+      </c>
+      <c r="K158" s="19" t="n">
+        <v>6.85</v>
+      </c>
+      <c r="L158" s="20" t="n">
+        <v>12</v>
+      </c>
+      <c r="M158" s="17" t="inlineStr">
+        <is>
+          <t>DE</t>
+        </is>
+      </c>
+      <c r="N158" s="21" t="n">
+        <v>12</v>
+      </c>
+      <c r="O158" s="19" t="n"/>
+      <c r="P158" s="13" t="inlineStr">
+        <is>
+          <t>Ativo</t>
+        </is>
+      </c>
+      <c r="Q158" s="13" t="inlineStr">
+        <is>
+          <t>Adimplente</t>
+        </is>
+      </c>
+      <c r="R158" s="22" t="inlineStr"/>
+    </row>
+    <row r="159" ht="16" customHeight="1">
+      <c r="A159" s="6" t="inlineStr">
+        <is>
+          <t>SOLANGE SILVA DE JESUS</t>
+        </is>
+      </c>
+      <c r="B159" s="7" t="n">
+        <v>1602.96</v>
+      </c>
+      <c r="C159" s="8" t="inlineStr">
+        <is>
+          <t>TOKIO MARINE</t>
+        </is>
+      </c>
+      <c r="D159" s="8" t="inlineStr">
+        <is>
+          <t>I30</t>
+        </is>
+      </c>
+      <c r="E159" s="9" t="n">
+        <v>20</v>
+      </c>
+      <c r="F159" s="10" t="n">
+        <v>320.59</v>
+      </c>
+      <c r="G159" s="10" t="n">
+        <v>83.34999999999999</v>
+      </c>
+      <c r="H159" s="10" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="I159" s="10" t="n">
+        <v>81.69</v>
+      </c>
+      <c r="J159" s="8" t="n">
+        <v>12</v>
+      </c>
+      <c r="K159" s="10" t="n">
+        <v>6.81</v>
+      </c>
+      <c r="L159" s="23" t="n">
+        <v>8</v>
+      </c>
+      <c r="M159" s="8" t="inlineStr">
+        <is>
+          <t>DE</t>
+        </is>
+      </c>
+      <c r="N159" s="12" t="n">
+        <v>12</v>
+      </c>
+      <c r="O159" s="10" t="n"/>
+      <c r="P159" s="13" t="inlineStr">
+        <is>
+          <t>Ativo</t>
+        </is>
+      </c>
+      <c r="Q159" s="13" t="inlineStr">
+        <is>
+          <t>Adimplente</t>
+        </is>
+      </c>
+      <c r="R159" s="14" t="inlineStr"/>
+    </row>
+    <row r="160" ht="16" customHeight="1">
+      <c r="A160" s="15" t="inlineStr">
+        <is>
+          <t>ROSANGELA DE JESUS MELO</t>
+        </is>
+      </c>
+      <c r="B160" s="16" t="n">
+        <v>1454.42</v>
+      </c>
+      <c r="C160" s="17" t="inlineStr">
+        <is>
+          <t>SUHAI</t>
+        </is>
+      </c>
+      <c r="D160" s="17" t="inlineStr">
+        <is>
+          <t>IDEA</t>
+        </is>
+      </c>
+      <c r="E160" s="18" t="n">
+        <v>25</v>
+      </c>
+      <c r="F160" s="19" t="n">
+        <v>363.61</v>
+      </c>
+      <c r="G160" s="19" t="n">
+        <v>94.54000000000001</v>
+      </c>
+      <c r="H160" s="19" t="n">
+        <v>1.89</v>
+      </c>
+      <c r="I160" s="19" t="n">
+        <v>92.65000000000001</v>
+      </c>
+      <c r="J160" s="17" t="n">
+        <v>1</v>
+      </c>
+      <c r="K160" s="19" t="n">
+        <v>92.65000000000001</v>
+      </c>
+      <c r="L160" s="24" t="n">
+        <v>6</v>
+      </c>
+      <c r="M160" s="17" t="inlineStr">
+        <is>
+          <t>DE</t>
+        </is>
+      </c>
+      <c r="N160" s="21" t="n">
+        <v>1</v>
+      </c>
+      <c r="O160" s="19" t="n"/>
+      <c r="P160" s="13" t="inlineStr">
+        <is>
+          <t>Ativo</t>
+        </is>
+      </c>
+      <c r="Q160" s="13" t="inlineStr">
+        <is>
+          <t>Adimplente</t>
+        </is>
+      </c>
+      <c r="R160" s="22" t="inlineStr"/>
+    </row>
+    <row r="161" ht="16" customHeight="1">
+      <c r="A161" s="6" t="inlineStr">
+        <is>
+          <t>ANTONIO CARLOS DOS SANTOS</t>
+        </is>
+      </c>
+      <c r="B161" s="7" t="n">
+        <v>2201.31</v>
+      </c>
+      <c r="C161" s="8" t="inlineStr">
+        <is>
+          <t>PORTO</t>
+        </is>
+      </c>
+      <c r="D161" s="8" t="inlineStr">
+        <is>
+          <t>TUCSON</t>
+        </is>
+      </c>
+      <c r="E161" s="9" t="n">
+        <v>18</v>
+      </c>
+      <c r="F161" s="10" t="n">
+        <v>396.24</v>
+      </c>
+      <c r="G161" s="10" t="n">
+        <v>103.02</v>
+      </c>
+      <c r="H161" s="10" t="n">
+        <v>2.06</v>
+      </c>
+      <c r="I161" s="10" t="n">
+        <v>100.96</v>
+      </c>
+      <c r="J161" s="8" t="n">
+        <v>10</v>
+      </c>
+      <c r="K161" s="10" t="n">
+        <v>10.1</v>
+      </c>
+      <c r="L161" s="23" t="n">
+        <v>6</v>
+      </c>
+      <c r="M161" s="8" t="inlineStr">
+        <is>
+          <t>DE</t>
+        </is>
+      </c>
+      <c r="N161" s="12" t="n">
+        <v>10</v>
+      </c>
+      <c r="O161" s="10" t="n"/>
+      <c r="P161" s="13" t="inlineStr">
+        <is>
+          <t>Ativo</t>
+        </is>
+      </c>
+      <c r="Q161" s="13" t="inlineStr">
+        <is>
+          <t>Adimplente</t>
+        </is>
+      </c>
+      <c r="R161" s="14" t="inlineStr"/>
+    </row>
+    <row r="162" ht="16" customHeight="1">
+      <c r="A162" s="15" t="inlineStr">
+        <is>
+          <t>OTAVIANO DE JESUS</t>
+        </is>
+      </c>
+      <c r="B162" s="16" t="n">
+        <v>1854.88</v>
+      </c>
+      <c r="C162" s="17" t="inlineStr">
+        <is>
+          <t>PORTO</t>
+        </is>
+      </c>
+      <c r="D162" s="17" t="inlineStr">
+        <is>
+          <t>CORSA</t>
+        </is>
+      </c>
+      <c r="E162" s="18" t="n">
+        <v>18</v>
+      </c>
+      <c r="F162" s="19" t="n">
+        <v>333.88</v>
+      </c>
+      <c r="G162" s="19" t="n">
+        <v>86.81</v>
+      </c>
+      <c r="H162" s="19" t="n">
+        <v>1.74</v>
+      </c>
+      <c r="I162" s="19" t="n">
+        <v>85.06999999999999</v>
+      </c>
+      <c r="J162" s="17" t="n">
+        <v>10</v>
+      </c>
+      <c r="K162" s="19" t="n">
+        <v>8.51</v>
+      </c>
+      <c r="L162" s="24" t="n">
+        <v>6</v>
+      </c>
+      <c r="M162" s="17" t="inlineStr">
+        <is>
+          <t>DE</t>
+        </is>
+      </c>
+      <c r="N162" s="21" t="n">
+        <v>10</v>
+      </c>
+      <c r="O162" s="19" t="n"/>
+      <c r="P162" s="13" t="inlineStr">
+        <is>
+          <t>Ativo</t>
+        </is>
+      </c>
+      <c r="Q162" s="13" t="inlineStr">
+        <is>
+          <t>Adimplente</t>
+        </is>
+      </c>
+      <c r="R162" s="22" t="inlineStr"/>
+    </row>
+    <row r="163" ht="16" customHeight="1">
+      <c r="A163" s="6" t="inlineStr">
+        <is>
+          <t>LEONARDO VAZ DE FREITAS</t>
+        </is>
+      </c>
+      <c r="B163" s="7" t="n">
+        <v>1689.84</v>
+      </c>
+      <c r="C163" s="8" t="inlineStr">
+        <is>
+          <t>SUHAI</t>
+        </is>
+      </c>
+      <c r="D163" s="8" t="inlineStr">
+        <is>
+          <t>TUCSON</t>
+        </is>
+      </c>
+      <c r="E163" s="9" t="n">
+        <v>25</v>
+      </c>
+      <c r="F163" s="10" t="n">
+        <v>422.46</v>
+      </c>
+      <c r="G163" s="10" t="n">
+        <v>109.84</v>
+      </c>
+      <c r="H163" s="10" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="I163" s="10" t="n">
+        <v>107.64</v>
+      </c>
+      <c r="J163" s="8" t="n">
+        <v>12</v>
+      </c>
+      <c r="K163" s="10" t="n">
+        <v>8.970000000000001</v>
+      </c>
+      <c r="L163" s="23" t="n">
+        <v>6</v>
+      </c>
+      <c r="M163" s="8" t="inlineStr">
+        <is>
+          <t>DE</t>
+        </is>
+      </c>
+      <c r="N163" s="12" t="n">
+        <v>12</v>
+      </c>
+      <c r="O163" s="10" t="n"/>
+      <c r="P163" s="13" t="inlineStr">
+        <is>
+          <t>Ativo</t>
+        </is>
+      </c>
+      <c r="Q163" s="13" t="inlineStr">
+        <is>
+          <t>Adimplente</t>
+        </is>
+      </c>
+      <c r="R163" s="14" t="inlineStr"/>
+    </row>
+    <row r="164" ht="16" customHeight="1">
+      <c r="A164" s="15" t="inlineStr">
+        <is>
+          <t>VALDISLEI XAVIER DO NASCIMENTO</t>
+        </is>
+      </c>
+      <c r="B164" s="16" t="n">
+        <v>4204.31</v>
+      </c>
+      <c r="C164" s="17" t="inlineStr">
+        <is>
+          <t>BRADESCO</t>
+        </is>
+      </c>
+      <c r="D164" s="17" t="inlineStr">
+        <is>
+          <t>COROLLA</t>
+        </is>
+      </c>
+      <c r="E164" s="18" t="n">
+        <v>20</v>
+      </c>
+      <c r="F164" s="19" t="n">
+        <v>840.86</v>
+      </c>
+      <c r="G164" s="19" t="n">
+        <v>218.62</v>
+      </c>
+      <c r="H164" s="19" t="n">
+        <v>4.37</v>
+      </c>
+      <c r="I164" s="19" t="n">
+        <v>214.25</v>
+      </c>
+      <c r="J164" s="17" t="n">
+        <v>10</v>
+      </c>
+      <c r="K164" s="19" t="n">
+        <v>21.43</v>
+      </c>
+      <c r="L164" s="24" t="n">
+        <v>5</v>
+      </c>
+      <c r="M164" s="17" t="inlineStr">
+        <is>
+          <t>DE</t>
+        </is>
+      </c>
+      <c r="N164" s="21" t="n">
+        <v>10</v>
+      </c>
+      <c r="O164" s="19" t="n"/>
+      <c r="P164" s="13" t="inlineStr">
+        <is>
+          <t>Ativo</t>
+        </is>
+      </c>
+      <c r="Q164" s="13" t="inlineStr">
+        <is>
+          <t>Adimplente</t>
+        </is>
+      </c>
+      <c r="R164" s="22" t="inlineStr"/>
+    </row>
+    <row r="165" ht="16" customHeight="1">
+      <c r="A165" s="6" t="inlineStr">
+        <is>
+          <t>DERANILDA PEREIRA COELHO</t>
+        </is>
+      </c>
+      <c r="B165" s="7" t="n">
+        <v>1553.27</v>
+      </c>
+      <c r="C165" s="8" t="inlineStr">
+        <is>
+          <t>SUHAI</t>
+        </is>
+      </c>
+      <c r="D165" s="8" t="inlineStr">
+        <is>
+          <t>ZARIFA</t>
+        </is>
+      </c>
+      <c r="E165" s="9" t="n">
+        <v>20</v>
+      </c>
+      <c r="F165" s="10" t="n">
+        <v>310.65</v>
+      </c>
+      <c r="G165" s="10" t="n">
+        <v>80.77</v>
+      </c>
+      <c r="H165" s="10" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="I165" s="10" t="n">
+        <v>79.15000000000001</v>
+      </c>
+      <c r="J165" s="8" t="n">
+        <v>5</v>
+      </c>
+      <c r="K165" s="10" t="n">
+        <v>15.83</v>
+      </c>
+      <c r="L165" s="11" t="n">
+        <v>5</v>
+      </c>
+      <c r="M165" s="8" t="inlineStr">
+        <is>
+          <t>DE</t>
+        </is>
+      </c>
+      <c r="N165" s="12" t="n">
+        <v>5</v>
+      </c>
+      <c r="O165" s="10" t="n"/>
+      <c r="P165" s="13" t="inlineStr">
+        <is>
+          <t>Ativo</t>
+        </is>
+      </c>
+      <c r="Q165" s="13" t="inlineStr">
+        <is>
+          <t>Adimplente</t>
+        </is>
+      </c>
+      <c r="R165" s="14" t="inlineStr"/>
+    </row>
+    <row r="166" ht="16" customHeight="1">
+      <c r="A166" s="15" t="inlineStr">
+        <is>
+          <t>IVO REIS DO NASCIMENTO</t>
+        </is>
+      </c>
+      <c r="B166" s="16" t="n">
+        <v>1199.51</v>
+      </c>
+      <c r="C166" s="17" t="inlineStr">
+        <is>
+          <t>AZUL</t>
+        </is>
+      </c>
+      <c r="D166" s="17" t="inlineStr">
+        <is>
+          <t>CITY SEDAN</t>
+        </is>
+      </c>
+      <c r="E166" s="18" t="n">
+        <v>20</v>
+      </c>
+      <c r="F166" s="19" t="n">
+        <v>239.9</v>
+      </c>
+      <c r="G166" s="19" t="n">
+        <v>62.37</v>
+      </c>
+      <c r="H166" s="19" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="I166" s="19" t="n">
+        <v>61.13</v>
+      </c>
+      <c r="J166" s="17" t="n">
+        <v>1</v>
+      </c>
+      <c r="K166" s="19" t="n">
+        <v>61.13</v>
+      </c>
+      <c r="L166" s="24" t="n">
+        <v>5</v>
+      </c>
+      <c r="M166" s="17" t="inlineStr">
+        <is>
+          <t>DE</t>
+        </is>
+      </c>
+      <c r="N166" s="21" t="n">
+        <v>1</v>
+      </c>
+      <c r="O166" s="19" t="n"/>
+      <c r="P166" s="13" t="inlineStr">
+        <is>
+          <t>Ativo</t>
+        </is>
+      </c>
+      <c r="Q166" s="13" t="inlineStr">
+        <is>
+          <t>Adimplente</t>
+        </is>
+      </c>
+      <c r="R166" s="22" t="inlineStr"/>
+    </row>
+    <row r="167" ht="16" customHeight="1">
+      <c r="A167" s="6" t="inlineStr">
+        <is>
+          <t>ANDREA NASCIMENTO SANTANA MARTIENA</t>
+        </is>
+      </c>
+      <c r="B167" s="7" t="n">
+        <v>1986.95</v>
+      </c>
+      <c r="C167" s="8" t="inlineStr">
+        <is>
+          <t>TOKIO MARINE</t>
+        </is>
+      </c>
+      <c r="D167" s="8" t="inlineStr">
+        <is>
+          <t>CRETA</t>
+        </is>
+      </c>
+      <c r="E167" s="9" t="n">
+        <v>20</v>
+      </c>
+      <c r="F167" s="10" t="n">
+        <v>397.39</v>
+      </c>
+      <c r="G167" s="10" t="n">
+        <v>103.32</v>
+      </c>
+      <c r="H167" s="10" t="n">
+        <v>2.07</v>
+      </c>
+      <c r="I167" s="10" t="n">
+        <v>101.25</v>
+      </c>
+      <c r="J167" s="8" t="n">
+        <v>12</v>
+      </c>
+      <c r="K167" s="10" t="n">
+        <v>8.44</v>
+      </c>
+      <c r="L167" s="23" t="n">
+        <v>5</v>
+      </c>
+      <c r="M167" s="8" t="inlineStr">
+        <is>
+          <t>DE</t>
+        </is>
+      </c>
+      <c r="N167" s="12" t="n">
+        <v>12</v>
+      </c>
+      <c r="O167" s="10" t="n"/>
+      <c r="P167" s="13" t="inlineStr">
+        <is>
+          <t>Ativo</t>
+        </is>
+      </c>
+      <c r="Q167" s="13" t="inlineStr">
+        <is>
+          <t>Adimplente</t>
+        </is>
+      </c>
+      <c r="R167" s="14" t="inlineStr"/>
+    </row>
+    <row r="168" ht="16" customHeight="1">
+      <c r="A168" s="15" t="inlineStr">
+        <is>
+          <t>CAIO CESAR DOS SANTOS</t>
+        </is>
+      </c>
+      <c r="B168" s="16" t="n">
+        <v>3310.55</v>
+      </c>
+      <c r="C168" s="17" t="inlineStr">
+        <is>
+          <t>SUHAI</t>
+        </is>
+      </c>
+      <c r="D168" s="17" t="inlineStr">
+        <is>
+          <t>SIENA</t>
+        </is>
+      </c>
+      <c r="E168" s="18" t="n">
+        <v>20</v>
+      </c>
+      <c r="F168" s="19" t="n">
+        <v>662.11</v>
+      </c>
+      <c r="G168" s="19" t="n">
+        <v>172.15</v>
+      </c>
+      <c r="H168" s="19" t="n">
+        <v>3.44</v>
+      </c>
+      <c r="I168" s="19" t="n">
+        <v>168.71</v>
+      </c>
+      <c r="J168" s="17" t="n">
+        <v>12</v>
+      </c>
+      <c r="K168" s="19" t="n">
+        <v>14.06</v>
+      </c>
+      <c r="L168" s="24" t="n">
+        <v>4</v>
+      </c>
+      <c r="M168" s="17" t="inlineStr">
+        <is>
+          <t>DE</t>
+        </is>
+      </c>
+      <c r="N168" s="21" t="n">
+        <v>12</v>
+      </c>
+      <c r="O168" s="19" t="n"/>
+      <c r="P168" s="13" t="inlineStr">
+        <is>
+          <t>Ativo</t>
+        </is>
+      </c>
+      <c r="Q168" s="13" t="inlineStr">
+        <is>
+          <t>Adimplente</t>
+        </is>
+      </c>
+      <c r="R168" s="22" t="inlineStr"/>
+    </row>
+    <row r="169" ht="16" customHeight="1">
+      <c r="A169" s="6" t="inlineStr">
+        <is>
+          <t>IVO REIS DO NASCIMENTO</t>
+        </is>
+      </c>
+      <c r="B169" s="7" t="n">
+        <v>2141.74</v>
+      </c>
+      <c r="C169" s="8" t="inlineStr">
+        <is>
+          <t>MITSUI</t>
+        </is>
+      </c>
+      <c r="D169" s="8" t="inlineStr">
+        <is>
+          <t>FOX</t>
+        </is>
+      </c>
+      <c r="E169" s="9" t="n">
+        <v>20</v>
+      </c>
+      <c r="F169" s="10" t="n">
+        <v>428.35</v>
+      </c>
+      <c r="G169" s="10" t="n">
+        <v>111.37</v>
+      </c>
+      <c r="H169" s="10" t="n">
+        <v>2.23</v>
+      </c>
+      <c r="I169" s="10" t="n">
+        <v>109.14</v>
+      </c>
+      <c r="J169" s="8" t="n">
+        <v>10</v>
+      </c>
+      <c r="K169" s="10" t="n">
+        <v>10.91</v>
+      </c>
+      <c r="L169" s="23" t="n">
+        <v>4</v>
+      </c>
+      <c r="M169" s="8" t="inlineStr">
+        <is>
+          <t>DE</t>
+        </is>
+      </c>
+      <c r="N169" s="12" t="n">
+        <v>10</v>
+      </c>
+      <c r="O169" s="10" t="n"/>
+      <c r="P169" s="13" t="inlineStr">
+        <is>
+          <t>Ativo</t>
+        </is>
+      </c>
+      <c r="Q169" s="13" t="inlineStr">
+        <is>
+          <t>Adimplente</t>
+        </is>
+      </c>
+      <c r="R169" s="14" t="inlineStr"/>
+    </row>
+    <row r="170" ht="16" customHeight="1">
+      <c r="A170" s="15" t="inlineStr">
+        <is>
+          <t>LEIDE DAYANE DE SOUZA</t>
+        </is>
+      </c>
+      <c r="B170" s="16" t="n">
+        <v>1642.98</v>
+      </c>
+      <c r="C170" s="17" t="inlineStr">
+        <is>
+          <t>ALIRO</t>
+        </is>
+      </c>
+      <c r="D170" s="17" t="inlineStr">
+        <is>
+          <t>ECOSPORT</t>
+        </is>
+      </c>
+      <c r="E170" s="18" t="n">
+        <v>20</v>
+      </c>
+      <c r="F170" s="19" t="n">
+        <v>328.6</v>
+      </c>
+      <c r="G170" s="19" t="n">
+        <v>85.43000000000001</v>
+      </c>
+      <c r="H170" s="19" t="n">
+        <v>1.71</v>
+      </c>
+      <c r="I170" s="19" t="n">
+        <v>83.73</v>
+      </c>
+      <c r="J170" s="17" t="n">
+        <v>10</v>
+      </c>
+      <c r="K170" s="19" t="n">
+        <v>8.369999999999999</v>
+      </c>
+      <c r="L170" s="24" t="n">
+        <v>4</v>
+      </c>
+      <c r="M170" s="17" t="inlineStr">
+        <is>
+          <t>DE</t>
+        </is>
+      </c>
+      <c r="N170" s="21" t="n">
+        <v>10</v>
+      </c>
+      <c r="O170" s="19" t="n"/>
+      <c r="P170" s="13" t="inlineStr">
+        <is>
+          <t>Ativo</t>
+        </is>
+      </c>
+      <c r="Q170" s="13" t="inlineStr">
+        <is>
+          <t>Adimplente</t>
+        </is>
+      </c>
+      <c r="R170" s="22" t="inlineStr"/>
+    </row>
+    <row r="171" ht="18" customHeight="1">
+      <c r="A171" s="25" t="inlineStr">
+        <is>
+          <t>TOTAL  NOV/25</t>
+        </is>
+      </c>
+      <c r="K171" s="26" t="n">
+        <v>323.21</v>
+      </c>
+      <c r="L171" s="27" t="n"/>
+      <c r="M171" s="27" t="n"/>
+      <c r="N171" s="27" t="n"/>
+      <c r="O171" s="27" t="n"/>
+      <c r="P171" s="27" t="n"/>
+      <c r="Q171" s="27" t="n"/>
+      <c r="R171" s="27" t="n"/>
+    </row>
+    <row r="173" ht="22" customHeight="1">
+      <c r="A173" s="3" t="inlineStr">
         <is>
           <t>dez/25</t>
         </is>
       </c>
-      <c r="B136" s="4" t="inlineStr">
+      <c r="B173" s="4" t="inlineStr">
         <is>
           <t>PRÊMIO LÍQ</t>
         </is>
       </c>
-      <c r="C136" s="4" t="inlineStr">
+      <c r="C173" s="4" t="inlineStr">
         <is>
           <t>SEGURADORA</t>
         </is>
       </c>
-      <c r="D136" s="4" t="inlineStr">
+      <c r="D173" s="4" t="inlineStr">
         <is>
           <t>ITEM</t>
         </is>
       </c>
-      <c r="E136" s="4" t="inlineStr">
+      <c r="E173" s="4" t="inlineStr">
         <is>
           <t>COM%</t>
         </is>
       </c>
-      <c r="F136" s="4" t="inlineStr">
+      <c r="F173" s="4" t="inlineStr">
         <is>
           <t>COMISSÃO</t>
         </is>
       </c>
-      <c r="G136" s="4" t="inlineStr">
+      <c r="G173" s="4" t="inlineStr">
         <is>
           <t>26%</t>
         </is>
       </c>
-      <c r="H136" s="4" t="inlineStr">
+      <c r="H173" s="4" t="inlineStr">
         <is>
           <t>2% DA</t>
         </is>
       </c>
-      <c r="I136" s="4" t="inlineStr">
+      <c r="I173" s="4" t="inlineStr">
         <is>
           <t>RECEBIDO</t>
         </is>
       </c>
-      <c r="J136" s="4" t="inlineStr">
+      <c r="J173" s="4" t="inlineStr">
         <is>
           <t>VEZES</t>
         </is>
       </c>
-      <c r="K136" s="4" t="inlineStr">
+      <c r="K173" s="4" t="inlineStr">
         <is>
           <t>RECEBER</t>
         </is>
       </c>
-      <c r="L136" s="5" t="inlineStr"/>
-      <c r="M136" s="4" t="inlineStr">
-        <is>
-          <t>DE</t>
-        </is>
-      </c>
-      <c r="N136" s="5" t="inlineStr"/>
-      <c r="O136" s="4" t="inlineStr">
+      <c r="L173" s="5" t="inlineStr"/>
+      <c r="M173" s="4" t="inlineStr">
+        <is>
+          <t>DE</t>
+        </is>
+      </c>
+      <c r="N173" s="5" t="inlineStr"/>
+      <c r="O173" s="4" t="inlineStr">
         <is>
           <t>AJUSTE</t>
         </is>
       </c>
-      <c r="P136" s="4" t="inlineStr">
+      <c r="P173" s="4" t="inlineStr">
         <is>
           <t>STATUS</t>
         </is>
       </c>
-      <c r="Q136" s="4" t="inlineStr">
+      <c r="Q173" s="4" t="inlineStr">
         <is>
           <t>ADIMPLÊNCIA</t>
         </is>
       </c>
-      <c r="R136" s="4" t="inlineStr">
+      <c r="R173" s="4" t="inlineStr">
         <is>
           <t>OBS</t>
         </is>
       </c>
     </row>
-    <row r="137" ht="16" customHeight="1">
-      <c r="A137" s="28" t="inlineStr">
-        <is>
-          <t>⚠  Dados de dez/25 ainda não inseridos — preencher manualmente</t>
-        </is>
-      </c>
-    </row>
-    <row r="139" ht="22" customHeight="1">
-      <c r="A139" s="3" t="inlineStr">
+    <row r="174" ht="16" customHeight="1">
+      <c r="A174" s="6" t="inlineStr">
+        <is>
+          <t>JULIO CESAR ALMEIDA DE OLIVEIRA</t>
+        </is>
+      </c>
+      <c r="B174" s="7" t="n">
+        <v>2089.08</v>
+      </c>
+      <c r="C174" s="8" t="inlineStr">
+        <is>
+          <t>TOKIO MARINE</t>
+        </is>
+      </c>
+      <c r="D174" s="8" t="inlineStr">
+        <is>
+          <t>I30</t>
+        </is>
+      </c>
+      <c r="E174" s="9" t="n">
+        <v>20</v>
+      </c>
+      <c r="F174" s="10" t="n">
+        <v>417.82</v>
+      </c>
+      <c r="G174" s="10" t="n">
+        <v>108.63</v>
+      </c>
+      <c r="H174" s="10" t="n">
+        <v>2.17</v>
+      </c>
+      <c r="I174" s="10" t="n">
+        <v>106.46</v>
+      </c>
+      <c r="J174" s="8" t="n">
+        <v>12</v>
+      </c>
+      <c r="K174" s="10" t="n">
+        <v>8.869999999999999</v>
+      </c>
+      <c r="L174" s="11" t="n">
+        <v>12</v>
+      </c>
+      <c r="M174" s="8" t="inlineStr">
+        <is>
+          <t>DE</t>
+        </is>
+      </c>
+      <c r="N174" s="12" t="n">
+        <v>12</v>
+      </c>
+      <c r="O174" s="10" t="n"/>
+      <c r="P174" s="13" t="inlineStr">
+        <is>
+          <t>Ativo</t>
+        </is>
+      </c>
+      <c r="Q174" s="13" t="inlineStr">
+        <is>
+          <t>Adimplente</t>
+        </is>
+      </c>
+      <c r="R174" s="14" t="inlineStr"/>
+    </row>
+    <row r="175" ht="16" customHeight="1">
+      <c r="A175" s="15" t="inlineStr">
+        <is>
+          <t>FRANCISCO FERNANDES DE LIMA</t>
+        </is>
+      </c>
+      <c r="B175" s="16" t="n">
+        <v>1752.74</v>
+      </c>
+      <c r="C175" s="17" t="inlineStr">
+        <is>
+          <t>ALIRO</t>
+        </is>
+      </c>
+      <c r="D175" s="17" t="inlineStr">
+        <is>
+          <t>CRETA</t>
+        </is>
+      </c>
+      <c r="E175" s="18" t="n">
+        <v>20</v>
+      </c>
+      <c r="F175" s="19" t="n">
+        <v>350.55</v>
+      </c>
+      <c r="G175" s="19" t="n">
+        <v>91.14</v>
+      </c>
+      <c r="H175" s="19" t="n">
+        <v>1.82</v>
+      </c>
+      <c r="I175" s="19" t="n">
+        <v>89.31999999999999</v>
+      </c>
+      <c r="J175" s="17" t="n">
+        <v>12</v>
+      </c>
+      <c r="K175" s="19" t="n">
+        <v>7.44</v>
+      </c>
+      <c r="L175" s="24" t="n">
+        <v>11</v>
+      </c>
+      <c r="M175" s="17" t="inlineStr">
+        <is>
+          <t>DE</t>
+        </is>
+      </c>
+      <c r="N175" s="21" t="n">
+        <v>12</v>
+      </c>
+      <c r="O175" s="19" t="n"/>
+      <c r="P175" s="13" t="inlineStr">
+        <is>
+          <t>Ativo</t>
+        </is>
+      </c>
+      <c r="Q175" s="13" t="inlineStr">
+        <is>
+          <t>Adimplente</t>
+        </is>
+      </c>
+      <c r="R175" s="22" t="inlineStr"/>
+    </row>
+    <row r="176" ht="16" customHeight="1">
+      <c r="A176" s="6" t="inlineStr">
+        <is>
+          <t>SOLANGE SILVA DE JESUS</t>
+        </is>
+      </c>
+      <c r="B176" s="7" t="n">
+        <v>1602.96</v>
+      </c>
+      <c r="C176" s="8" t="inlineStr">
+        <is>
+          <t>TOKIO MARINE</t>
+        </is>
+      </c>
+      <c r="D176" s="8" t="inlineStr">
+        <is>
+          <t>I30</t>
+        </is>
+      </c>
+      <c r="E176" s="9" t="n">
+        <v>20</v>
+      </c>
+      <c r="F176" s="10" t="n">
+        <v>320.59</v>
+      </c>
+      <c r="G176" s="10" t="n">
+        <v>83.34999999999999</v>
+      </c>
+      <c r="H176" s="10" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="I176" s="10" t="n">
+        <v>81.69</v>
+      </c>
+      <c r="J176" s="8" t="n">
+        <v>12</v>
+      </c>
+      <c r="K176" s="10" t="n">
+        <v>6.81</v>
+      </c>
+      <c r="L176" s="23" t="n">
+        <v>9</v>
+      </c>
+      <c r="M176" s="8" t="inlineStr">
+        <is>
+          <t>DE</t>
+        </is>
+      </c>
+      <c r="N176" s="12" t="n">
+        <v>12</v>
+      </c>
+      <c r="O176" s="10" t="n"/>
+      <c r="P176" s="13" t="inlineStr">
+        <is>
+          <t>Ativo</t>
+        </is>
+      </c>
+      <c r="Q176" s="13" t="inlineStr">
+        <is>
+          <t>Adimplente</t>
+        </is>
+      </c>
+      <c r="R176" s="14" t="inlineStr"/>
+    </row>
+    <row r="177" ht="16" customHeight="1">
+      <c r="A177" s="15" t="inlineStr">
+        <is>
+          <t>ROSANGELA DE JESUS MELO</t>
+        </is>
+      </c>
+      <c r="B177" s="16" t="n">
+        <v>1454.42</v>
+      </c>
+      <c r="C177" s="17" t="inlineStr">
+        <is>
+          <t>SUHAI</t>
+        </is>
+      </c>
+      <c r="D177" s="17" t="inlineStr">
+        <is>
+          <t>IDEA</t>
+        </is>
+      </c>
+      <c r="E177" s="18" t="n">
+        <v>25</v>
+      </c>
+      <c r="F177" s="19" t="n">
+        <v>363.61</v>
+      </c>
+      <c r="G177" s="19" t="n">
+        <v>94.54000000000001</v>
+      </c>
+      <c r="H177" s="19" t="n">
+        <v>1.89</v>
+      </c>
+      <c r="I177" s="19" t="n">
+        <v>92.65000000000001</v>
+      </c>
+      <c r="J177" s="17" t="n">
+        <v>1</v>
+      </c>
+      <c r="K177" s="19" t="n">
+        <v>92.65000000000001</v>
+      </c>
+      <c r="L177" s="24" t="n">
+        <v>7</v>
+      </c>
+      <c r="M177" s="17" t="inlineStr">
+        <is>
+          <t>DE</t>
+        </is>
+      </c>
+      <c r="N177" s="21" t="n">
+        <v>1</v>
+      </c>
+      <c r="O177" s="19" t="n"/>
+      <c r="P177" s="13" t="inlineStr">
+        <is>
+          <t>Ativo</t>
+        </is>
+      </c>
+      <c r="Q177" s="13" t="inlineStr">
+        <is>
+          <t>Adimplente</t>
+        </is>
+      </c>
+      <c r="R177" s="22" t="inlineStr"/>
+    </row>
+    <row r="178" ht="16" customHeight="1">
+      <c r="A178" s="6" t="inlineStr">
+        <is>
+          <t>ANTONIO CARLOS DOS SANTOS</t>
+        </is>
+      </c>
+      <c r="B178" s="7" t="n">
+        <v>2201.31</v>
+      </c>
+      <c r="C178" s="8" t="inlineStr">
+        <is>
+          <t>PORTO</t>
+        </is>
+      </c>
+      <c r="D178" s="8" t="inlineStr">
+        <is>
+          <t>TUCSON</t>
+        </is>
+      </c>
+      <c r="E178" s="9" t="n">
+        <v>18</v>
+      </c>
+      <c r="F178" s="10" t="n">
+        <v>396.24</v>
+      </c>
+      <c r="G178" s="10" t="n">
+        <v>103.02</v>
+      </c>
+      <c r="H178" s="10" t="n">
+        <v>2.06</v>
+      </c>
+      <c r="I178" s="10" t="n">
+        <v>100.96</v>
+      </c>
+      <c r="J178" s="8" t="n">
+        <v>10</v>
+      </c>
+      <c r="K178" s="10" t="n">
+        <v>10.1</v>
+      </c>
+      <c r="L178" s="23" t="n">
+        <v>7</v>
+      </c>
+      <c r="M178" s="8" t="inlineStr">
+        <is>
+          <t>DE</t>
+        </is>
+      </c>
+      <c r="N178" s="12" t="n">
+        <v>10</v>
+      </c>
+      <c r="O178" s="10" t="n"/>
+      <c r="P178" s="13" t="inlineStr">
+        <is>
+          <t>Ativo</t>
+        </is>
+      </c>
+      <c r="Q178" s="13" t="inlineStr">
+        <is>
+          <t>Adimplente</t>
+        </is>
+      </c>
+      <c r="R178" s="14" t="inlineStr"/>
+    </row>
+    <row r="179" ht="16" customHeight="1">
+      <c r="A179" s="15" t="inlineStr">
+        <is>
+          <t>OTAVIANO DE JESUS</t>
+        </is>
+      </c>
+      <c r="B179" s="16" t="n">
+        <v>1854.88</v>
+      </c>
+      <c r="C179" s="17" t="inlineStr">
+        <is>
+          <t>PORTO</t>
+        </is>
+      </c>
+      <c r="D179" s="17" t="inlineStr">
+        <is>
+          <t>CORSA</t>
+        </is>
+      </c>
+      <c r="E179" s="18" t="n">
+        <v>18</v>
+      </c>
+      <c r="F179" s="19" t="n">
+        <v>333.88</v>
+      </c>
+      <c r="G179" s="19" t="n">
+        <v>86.81</v>
+      </c>
+      <c r="H179" s="19" t="n">
+        <v>1.74</v>
+      </c>
+      <c r="I179" s="19" t="n">
+        <v>85.06999999999999</v>
+      </c>
+      <c r="J179" s="17" t="n">
+        <v>10</v>
+      </c>
+      <c r="K179" s="19" t="n">
+        <v>8.51</v>
+      </c>
+      <c r="L179" s="24" t="n">
+        <v>7</v>
+      </c>
+      <c r="M179" s="17" t="inlineStr">
+        <is>
+          <t>DE</t>
+        </is>
+      </c>
+      <c r="N179" s="21" t="n">
+        <v>10</v>
+      </c>
+      <c r="O179" s="19" t="n"/>
+      <c r="P179" s="13" t="inlineStr">
+        <is>
+          <t>Ativo</t>
+        </is>
+      </c>
+      <c r="Q179" s="13" t="inlineStr">
+        <is>
+          <t>Adimplente</t>
+        </is>
+      </c>
+      <c r="R179" s="22" t="inlineStr"/>
+    </row>
+    <row r="180" ht="16" customHeight="1">
+      <c r="A180" s="6" t="inlineStr">
+        <is>
+          <t>LEONARDO VAZ DE FREITAS</t>
+        </is>
+      </c>
+      <c r="B180" s="7" t="n">
+        <v>1689.84</v>
+      </c>
+      <c r="C180" s="8" t="inlineStr">
+        <is>
+          <t>SUHAI</t>
+        </is>
+      </c>
+      <c r="D180" s="8" t="inlineStr">
+        <is>
+          <t>TUCSON</t>
+        </is>
+      </c>
+      <c r="E180" s="9" t="n">
+        <v>25</v>
+      </c>
+      <c r="F180" s="10" t="n">
+        <v>422.46</v>
+      </c>
+      <c r="G180" s="10" t="n">
+        <v>109.84</v>
+      </c>
+      <c r="H180" s="10" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="I180" s="10" t="n">
+        <v>107.64</v>
+      </c>
+      <c r="J180" s="8" t="n">
+        <v>12</v>
+      </c>
+      <c r="K180" s="10" t="n">
+        <v>8.970000000000001</v>
+      </c>
+      <c r="L180" s="23" t="n">
+        <v>7</v>
+      </c>
+      <c r="M180" s="8" t="inlineStr">
+        <is>
+          <t>DE</t>
+        </is>
+      </c>
+      <c r="N180" s="12" t="n">
+        <v>12</v>
+      </c>
+      <c r="O180" s="10" t="n"/>
+      <c r="P180" s="13" t="inlineStr">
+        <is>
+          <t>Ativo</t>
+        </is>
+      </c>
+      <c r="Q180" s="13" t="inlineStr">
+        <is>
+          <t>Adimplente</t>
+        </is>
+      </c>
+      <c r="R180" s="14" t="inlineStr"/>
+    </row>
+    <row r="181" ht="16" customHeight="1">
+      <c r="A181" s="15" t="inlineStr">
+        <is>
+          <t>VALDISLEI XAVIER DO NASCIMENTO</t>
+        </is>
+      </c>
+      <c r="B181" s="16" t="n">
+        <v>4204.31</v>
+      </c>
+      <c r="C181" s="17" t="inlineStr">
+        <is>
+          <t>BRADESCO</t>
+        </is>
+      </c>
+      <c r="D181" s="17" t="inlineStr">
+        <is>
+          <t>COROLLA</t>
+        </is>
+      </c>
+      <c r="E181" s="18" t="n">
+        <v>20</v>
+      </c>
+      <c r="F181" s="19" t="n">
+        <v>840.86</v>
+      </c>
+      <c r="G181" s="19" t="n">
+        <v>218.62</v>
+      </c>
+      <c r="H181" s="19" t="n">
+        <v>4.37</v>
+      </c>
+      <c r="I181" s="19" t="n">
+        <v>214.25</v>
+      </c>
+      <c r="J181" s="17" t="n">
+        <v>10</v>
+      </c>
+      <c r="K181" s="19" t="n">
+        <v>21.43</v>
+      </c>
+      <c r="L181" s="24" t="n">
+        <v>6</v>
+      </c>
+      <c r="M181" s="17" t="inlineStr">
+        <is>
+          <t>DE</t>
+        </is>
+      </c>
+      <c r="N181" s="21" t="n">
+        <v>10</v>
+      </c>
+      <c r="O181" s="19" t="n"/>
+      <c r="P181" s="13" t="inlineStr">
+        <is>
+          <t>Ativo</t>
+        </is>
+      </c>
+      <c r="Q181" s="13" t="inlineStr">
+        <is>
+          <t>Adimplente</t>
+        </is>
+      </c>
+      <c r="R181" s="22" t="inlineStr"/>
+    </row>
+    <row r="182" ht="16" customHeight="1">
+      <c r="A182" s="6" t="inlineStr">
+        <is>
+          <t>IVO REIS DO NASCIMENTO</t>
+        </is>
+      </c>
+      <c r="B182" s="7" t="n">
+        <v>1199.51</v>
+      </c>
+      <c r="C182" s="8" t="inlineStr">
+        <is>
+          <t>AZUL</t>
+        </is>
+      </c>
+      <c r="D182" s="8" t="inlineStr">
+        <is>
+          <t>CITY SEDAN</t>
+        </is>
+      </c>
+      <c r="E182" s="9" t="n">
+        <v>20</v>
+      </c>
+      <c r="F182" s="10" t="n">
+        <v>239.9</v>
+      </c>
+      <c r="G182" s="10" t="n">
+        <v>62.37</v>
+      </c>
+      <c r="H182" s="10" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="I182" s="10" t="n">
+        <v>61.13</v>
+      </c>
+      <c r="J182" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="K182" s="10" t="n">
+        <v>61.13</v>
+      </c>
+      <c r="L182" s="23" t="n">
+        <v>6</v>
+      </c>
+      <c r="M182" s="8" t="inlineStr">
+        <is>
+          <t>DE</t>
+        </is>
+      </c>
+      <c r="N182" s="12" t="n">
+        <v>1</v>
+      </c>
+      <c r="O182" s="10" t="n"/>
+      <c r="P182" s="13" t="inlineStr">
+        <is>
+          <t>Ativo</t>
+        </is>
+      </c>
+      <c r="Q182" s="13" t="inlineStr">
+        <is>
+          <t>Adimplente</t>
+        </is>
+      </c>
+      <c r="R182" s="14" t="inlineStr"/>
+    </row>
+    <row r="183" ht="16" customHeight="1">
+      <c r="A183" s="15" t="inlineStr">
+        <is>
+          <t>ANDREA NASCIMENTO SANTANA MARTIENA</t>
+        </is>
+      </c>
+      <c r="B183" s="16" t="n">
+        <v>1986.95</v>
+      </c>
+      <c r="C183" s="17" t="inlineStr">
+        <is>
+          <t>TOKIO MARINE</t>
+        </is>
+      </c>
+      <c r="D183" s="17" t="inlineStr">
+        <is>
+          <t>CRETA</t>
+        </is>
+      </c>
+      <c r="E183" s="18" t="n">
+        <v>20</v>
+      </c>
+      <c r="F183" s="19" t="n">
+        <v>397.39</v>
+      </c>
+      <c r="G183" s="19" t="n">
+        <v>103.32</v>
+      </c>
+      <c r="H183" s="19" t="n">
+        <v>2.07</v>
+      </c>
+      <c r="I183" s="19" t="n">
+        <v>101.25</v>
+      </c>
+      <c r="J183" s="17" t="n">
+        <v>12</v>
+      </c>
+      <c r="K183" s="19" t="n">
+        <v>8.44</v>
+      </c>
+      <c r="L183" s="24" t="n">
+        <v>6</v>
+      </c>
+      <c r="M183" s="17" t="inlineStr">
+        <is>
+          <t>DE</t>
+        </is>
+      </c>
+      <c r="N183" s="21" t="n">
+        <v>12</v>
+      </c>
+      <c r="O183" s="19" t="n"/>
+      <c r="P183" s="13" t="inlineStr">
+        <is>
+          <t>Ativo</t>
+        </is>
+      </c>
+      <c r="Q183" s="13" t="inlineStr">
+        <is>
+          <t>Adimplente</t>
+        </is>
+      </c>
+      <c r="R183" s="22" t="inlineStr"/>
+    </row>
+    <row r="184" ht="16" customHeight="1">
+      <c r="A184" s="6" t="inlineStr">
+        <is>
+          <t>CAIO CESAR DOS SANTOS</t>
+        </is>
+      </c>
+      <c r="B184" s="7" t="n">
+        <v>3310.55</v>
+      </c>
+      <c r="C184" s="8" t="inlineStr">
+        <is>
+          <t>SUHAI</t>
+        </is>
+      </c>
+      <c r="D184" s="8" t="inlineStr">
+        <is>
+          <t>SIENA</t>
+        </is>
+      </c>
+      <c r="E184" s="9" t="n">
+        <v>20</v>
+      </c>
+      <c r="F184" s="10" t="n">
+        <v>662.11</v>
+      </c>
+      <c r="G184" s="10" t="n">
+        <v>172.15</v>
+      </c>
+      <c r="H184" s="10" t="n">
+        <v>3.44</v>
+      </c>
+      <c r="I184" s="10" t="n">
+        <v>168.71</v>
+      </c>
+      <c r="J184" s="8" t="n">
+        <v>12</v>
+      </c>
+      <c r="K184" s="10" t="n">
+        <v>14.06</v>
+      </c>
+      <c r="L184" s="23" t="n">
+        <v>5</v>
+      </c>
+      <c r="M184" s="8" t="inlineStr">
+        <is>
+          <t>DE</t>
+        </is>
+      </c>
+      <c r="N184" s="12" t="n">
+        <v>12</v>
+      </c>
+      <c r="O184" s="10" t="n"/>
+      <c r="P184" s="13" t="inlineStr">
+        <is>
+          <t>Ativo</t>
+        </is>
+      </c>
+      <c r="Q184" s="13" t="inlineStr">
+        <is>
+          <t>Adimplente</t>
+        </is>
+      </c>
+      <c r="R184" s="14" t="inlineStr"/>
+    </row>
+    <row r="185" ht="16" customHeight="1">
+      <c r="A185" s="15" t="inlineStr">
+        <is>
+          <t>IVO REIS DO NASCIMENTO</t>
+        </is>
+      </c>
+      <c r="B185" s="16" t="n">
+        <v>2141.74</v>
+      </c>
+      <c r="C185" s="17" t="inlineStr">
+        <is>
+          <t>MITSUI</t>
+        </is>
+      </c>
+      <c r="D185" s="17" t="inlineStr">
+        <is>
+          <t>FOX</t>
+        </is>
+      </c>
+      <c r="E185" s="18" t="n">
+        <v>20</v>
+      </c>
+      <c r="F185" s="19" t="n">
+        <v>428.35</v>
+      </c>
+      <c r="G185" s="19" t="n">
+        <v>111.37</v>
+      </c>
+      <c r="H185" s="19" t="n">
+        <v>2.23</v>
+      </c>
+      <c r="I185" s="19" t="n">
+        <v>109.14</v>
+      </c>
+      <c r="J185" s="17" t="n">
+        <v>10</v>
+      </c>
+      <c r="K185" s="19" t="n">
+        <v>10.91</v>
+      </c>
+      <c r="L185" s="24" t="n">
+        <v>5</v>
+      </c>
+      <c r="M185" s="17" t="inlineStr">
+        <is>
+          <t>DE</t>
+        </is>
+      </c>
+      <c r="N185" s="21" t="n">
+        <v>10</v>
+      </c>
+      <c r="O185" s="19" t="n"/>
+      <c r="P185" s="13" t="inlineStr">
+        <is>
+          <t>Ativo</t>
+        </is>
+      </c>
+      <c r="Q185" s="13" t="inlineStr">
+        <is>
+          <t>Adimplente</t>
+        </is>
+      </c>
+      <c r="R185" s="22" t="inlineStr"/>
+    </row>
+    <row r="186" ht="16" customHeight="1">
+      <c r="A186" s="6" t="inlineStr">
+        <is>
+          <t>LEIDE DAYANE DE SOUZA</t>
+        </is>
+      </c>
+      <c r="B186" s="7" t="n">
+        <v>1642.98</v>
+      </c>
+      <c r="C186" s="8" t="inlineStr">
+        <is>
+          <t>ALIRO</t>
+        </is>
+      </c>
+      <c r="D186" s="8" t="inlineStr">
+        <is>
+          <t>ECOSPORT</t>
+        </is>
+      </c>
+      <c r="E186" s="9" t="n">
+        <v>20</v>
+      </c>
+      <c r="F186" s="10" t="n">
+        <v>328.6</v>
+      </c>
+      <c r="G186" s="10" t="n">
+        <v>85.43000000000001</v>
+      </c>
+      <c r="H186" s="10" t="n">
+        <v>1.71</v>
+      </c>
+      <c r="I186" s="10" t="n">
+        <v>83.73</v>
+      </c>
+      <c r="J186" s="8" t="n">
+        <v>10</v>
+      </c>
+      <c r="K186" s="10" t="n">
+        <v>8.369999999999999</v>
+      </c>
+      <c r="L186" s="23" t="n">
+        <v>5</v>
+      </c>
+      <c r="M186" s="8" t="inlineStr">
+        <is>
+          <t>DE</t>
+        </is>
+      </c>
+      <c r="N186" s="12" t="n">
+        <v>10</v>
+      </c>
+      <c r="O186" s="10" t="n"/>
+      <c r="P186" s="13" t="inlineStr">
+        <is>
+          <t>Ativo</t>
+        </is>
+      </c>
+      <c r="Q186" s="13" t="inlineStr">
+        <is>
+          <t>Adimplente</t>
+        </is>
+      </c>
+      <c r="R186" s="14" t="inlineStr"/>
+    </row>
+    <row r="187" ht="18" customHeight="1">
+      <c r="A187" s="25" t="inlineStr">
+        <is>
+          <t>TOTAL  DEZ/25</t>
+        </is>
+      </c>
+      <c r="K187" s="26" t="n">
+        <v>267.69</v>
+      </c>
+      <c r="L187" s="27" t="n"/>
+      <c r="M187" s="27" t="n"/>
+      <c r="N187" s="27" t="n"/>
+      <c r="O187" s="27" t="n"/>
+      <c r="P187" s="27" t="n"/>
+      <c r="Q187" s="27" t="n"/>
+      <c r="R187" s="27" t="n"/>
+    </row>
+    <row r="189" ht="22" customHeight="1">
+      <c r="A189" s="3" t="inlineStr">
         <is>
           <t>jan/26</t>
         </is>
       </c>
-      <c r="B139" s="4" t="inlineStr">
+      <c r="B189" s="4" t="inlineStr">
         <is>
           <t>PRÊMIO LÍQ</t>
         </is>
       </c>
-      <c r="C139" s="4" t="inlineStr">
+      <c r="C189" s="4" t="inlineStr">
         <is>
           <t>SEGURADORA</t>
         </is>
       </c>
-      <c r="D139" s="4" t="inlineStr">
+      <c r="D189" s="4" t="inlineStr">
         <is>
           <t>ITEM</t>
         </is>
       </c>
-      <c r="E139" s="4" t="inlineStr">
+      <c r="E189" s="4" t="inlineStr">
         <is>
           <t>COM%</t>
         </is>
       </c>
-      <c r="F139" s="4" t="inlineStr">
+      <c r="F189" s="4" t="inlineStr">
         <is>
           <t>COMISSÃO</t>
         </is>
       </c>
-      <c r="G139" s="4" t="inlineStr">
+      <c r="G189" s="4" t="inlineStr">
         <is>
           <t>26%</t>
         </is>
       </c>
-      <c r="H139" s="4" t="inlineStr">
+      <c r="H189" s="4" t="inlineStr">
         <is>
           <t>2% DA</t>
         </is>
       </c>
-      <c r="I139" s="4" t="inlineStr">
+      <c r="I189" s="4" t="inlineStr">
         <is>
           <t>RECEBIDO</t>
         </is>
       </c>
-      <c r="J139" s="4" t="inlineStr">
+      <c r="J189" s="4" t="inlineStr">
         <is>
           <t>VEZES</t>
         </is>
       </c>
-      <c r="K139" s="4" t="inlineStr">
+      <c r="K189" s="4" t="inlineStr">
         <is>
           <t>RECEBER</t>
         </is>
       </c>
-      <c r="L139" s="5" t="inlineStr"/>
-      <c r="M139" s="4" t="inlineStr">
-        <is>
-          <t>DE</t>
-        </is>
-      </c>
-      <c r="N139" s="5" t="inlineStr"/>
-      <c r="O139" s="4" t="inlineStr">
+      <c r="L189" s="5" t="inlineStr"/>
+      <c r="M189" s="4" t="inlineStr">
+        <is>
+          <t>DE</t>
+        </is>
+      </c>
+      <c r="N189" s="5" t="inlineStr"/>
+      <c r="O189" s="4" t="inlineStr">
         <is>
           <t>AJUSTE</t>
         </is>
       </c>
-      <c r="P139" s="4" t="inlineStr">
+      <c r="P189" s="4" t="inlineStr">
         <is>
           <t>STATUS</t>
         </is>
       </c>
-      <c r="Q139" s="4" t="inlineStr">
+      <c r="Q189" s="4" t="inlineStr">
         <is>
           <t>ADIMPLÊNCIA</t>
         </is>
       </c>
-      <c r="R139" s="4" t="inlineStr">
+      <c r="R189" s="4" t="inlineStr">
         <is>
           <t>OBS</t>
         </is>
       </c>
     </row>
-    <row r="140" ht="16" customHeight="1">
-      <c r="A140" s="28" t="inlineStr">
-        <is>
-          <t>⚠  Dados de jan/26 ainda não inseridos — preencher manualmente</t>
-        </is>
-      </c>
-    </row>
-    <row r="142" ht="22" customHeight="1">
-      <c r="A142" s="3" t="inlineStr">
+    <row r="190" ht="16" customHeight="1">
+      <c r="A190" s="6" t="inlineStr">
+        <is>
+          <t>FRANCISCO FERNANDES DE LIMA</t>
+        </is>
+      </c>
+      <c r="B190" s="7" t="n">
+        <v>1752.74</v>
+      </c>
+      <c r="C190" s="8" t="inlineStr">
+        <is>
+          <t>ALIRO</t>
+        </is>
+      </c>
+      <c r="D190" s="8" t="inlineStr">
+        <is>
+          <t>CRETA</t>
+        </is>
+      </c>
+      <c r="E190" s="9" t="n">
+        <v>20</v>
+      </c>
+      <c r="F190" s="10" t="n">
+        <v>350.55</v>
+      </c>
+      <c r="G190" s="10" t="n">
+        <v>91.14</v>
+      </c>
+      <c r="H190" s="10" t="n">
+        <v>1.82</v>
+      </c>
+      <c r="I190" s="10" t="n">
+        <v>89.31999999999999</v>
+      </c>
+      <c r="J190" s="8" t="n">
+        <v>12</v>
+      </c>
+      <c r="K190" s="10" t="n">
+        <v>7.44</v>
+      </c>
+      <c r="L190" s="11" t="n">
+        <v>12</v>
+      </c>
+      <c r="M190" s="8" t="inlineStr">
+        <is>
+          <t>DE</t>
+        </is>
+      </c>
+      <c r="N190" s="12" t="n">
+        <v>12</v>
+      </c>
+      <c r="O190" s="10" t="n"/>
+      <c r="P190" s="13" t="inlineStr">
+        <is>
+          <t>Ativo</t>
+        </is>
+      </c>
+      <c r="Q190" s="13" t="inlineStr">
+        <is>
+          <t>Adimplente</t>
+        </is>
+      </c>
+      <c r="R190" s="14" t="inlineStr"/>
+    </row>
+    <row r="191" ht="16" customHeight="1">
+      <c r="A191" s="15" t="inlineStr">
+        <is>
+          <t>SOLANGE SILVA DE JESUS</t>
+        </is>
+      </c>
+      <c r="B191" s="16" t="n">
+        <v>1602.96</v>
+      </c>
+      <c r="C191" s="17" t="inlineStr">
+        <is>
+          <t>TOKIO MARINE</t>
+        </is>
+      </c>
+      <c r="D191" s="17" t="inlineStr">
+        <is>
+          <t>I30</t>
+        </is>
+      </c>
+      <c r="E191" s="18" t="n">
+        <v>20</v>
+      </c>
+      <c r="F191" s="19" t="n">
+        <v>320.59</v>
+      </c>
+      <c r="G191" s="19" t="n">
+        <v>83.34999999999999</v>
+      </c>
+      <c r="H191" s="19" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="I191" s="19" t="n">
+        <v>81.69</v>
+      </c>
+      <c r="J191" s="17" t="n">
+        <v>12</v>
+      </c>
+      <c r="K191" s="19" t="n">
+        <v>6.81</v>
+      </c>
+      <c r="L191" s="24" t="n">
+        <v>10</v>
+      </c>
+      <c r="M191" s="17" t="inlineStr">
+        <is>
+          <t>DE</t>
+        </is>
+      </c>
+      <c r="N191" s="21" t="n">
+        <v>12</v>
+      </c>
+      <c r="O191" s="19" t="n"/>
+      <c r="P191" s="13" t="inlineStr">
+        <is>
+          <t>Ativo</t>
+        </is>
+      </c>
+      <c r="Q191" s="13" t="inlineStr">
+        <is>
+          <t>Adimplente</t>
+        </is>
+      </c>
+      <c r="R191" s="22" t="inlineStr"/>
+    </row>
+    <row r="192" ht="16" customHeight="1">
+      <c r="A192" s="6" t="inlineStr">
+        <is>
+          <t>ROSANGELA DE JESUS MELO</t>
+        </is>
+      </c>
+      <c r="B192" s="7" t="n">
+        <v>1454.42</v>
+      </c>
+      <c r="C192" s="8" t="inlineStr">
+        <is>
+          <t>SUHAI</t>
+        </is>
+      </c>
+      <c r="D192" s="8" t="inlineStr">
+        <is>
+          <t>IDEA</t>
+        </is>
+      </c>
+      <c r="E192" s="9" t="n">
+        <v>25</v>
+      </c>
+      <c r="F192" s="10" t="n">
+        <v>363.61</v>
+      </c>
+      <c r="G192" s="10" t="n">
+        <v>94.54000000000001</v>
+      </c>
+      <c r="H192" s="10" t="n">
+        <v>1.89</v>
+      </c>
+      <c r="I192" s="10" t="n">
+        <v>92.65000000000001</v>
+      </c>
+      <c r="J192" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="K192" s="10" t="n">
+        <v>92.65000000000001</v>
+      </c>
+      <c r="L192" s="23" t="n">
+        <v>8</v>
+      </c>
+      <c r="M192" s="8" t="inlineStr">
+        <is>
+          <t>DE</t>
+        </is>
+      </c>
+      <c r="N192" s="12" t="n">
+        <v>1</v>
+      </c>
+      <c r="O192" s="10" t="n"/>
+      <c r="P192" s="13" t="inlineStr">
+        <is>
+          <t>Ativo</t>
+        </is>
+      </c>
+      <c r="Q192" s="13" t="inlineStr">
+        <is>
+          <t>Adimplente</t>
+        </is>
+      </c>
+      <c r="R192" s="14" t="inlineStr"/>
+    </row>
+    <row r="193" ht="16" customHeight="1">
+      <c r="A193" s="15" t="inlineStr">
+        <is>
+          <t>ANTONIO CARLOS DOS SANTOS</t>
+        </is>
+      </c>
+      <c r="B193" s="16" t="n">
+        <v>2201.31</v>
+      </c>
+      <c r="C193" s="17" t="inlineStr">
+        <is>
+          <t>PORTO</t>
+        </is>
+      </c>
+      <c r="D193" s="17" t="inlineStr">
+        <is>
+          <t>TUCSON</t>
+        </is>
+      </c>
+      <c r="E193" s="18" t="n">
+        <v>18</v>
+      </c>
+      <c r="F193" s="19" t="n">
+        <v>396.24</v>
+      </c>
+      <c r="G193" s="19" t="n">
+        <v>103.02</v>
+      </c>
+      <c r="H193" s="19" t="n">
+        <v>2.06</v>
+      </c>
+      <c r="I193" s="19" t="n">
+        <v>100.96</v>
+      </c>
+      <c r="J193" s="17" t="n">
+        <v>10</v>
+      </c>
+      <c r="K193" s="19" t="n">
+        <v>10.1</v>
+      </c>
+      <c r="L193" s="24" t="n">
+        <v>8</v>
+      </c>
+      <c r="M193" s="17" t="inlineStr">
+        <is>
+          <t>DE</t>
+        </is>
+      </c>
+      <c r="N193" s="21" t="n">
+        <v>10</v>
+      </c>
+      <c r="O193" s="19" t="n"/>
+      <c r="P193" s="13" t="inlineStr">
+        <is>
+          <t>Ativo</t>
+        </is>
+      </c>
+      <c r="Q193" s="13" t="inlineStr">
+        <is>
+          <t>Adimplente</t>
+        </is>
+      </c>
+      <c r="R193" s="22" t="inlineStr"/>
+    </row>
+    <row r="194" ht="16" customHeight="1">
+      <c r="A194" s="6" t="inlineStr">
+        <is>
+          <t>OTAVIANO DE JESUS</t>
+        </is>
+      </c>
+      <c r="B194" s="7" t="n">
+        <v>1854.88</v>
+      </c>
+      <c r="C194" s="8" t="inlineStr">
+        <is>
+          <t>PORTO</t>
+        </is>
+      </c>
+      <c r="D194" s="8" t="inlineStr">
+        <is>
+          <t>CORSA</t>
+        </is>
+      </c>
+      <c r="E194" s="9" t="n">
+        <v>18</v>
+      </c>
+      <c r="F194" s="10" t="n">
+        <v>333.88</v>
+      </c>
+      <c r="G194" s="10" t="n">
+        <v>86.81</v>
+      </c>
+      <c r="H194" s="10" t="n">
+        <v>1.74</v>
+      </c>
+      <c r="I194" s="10" t="n">
+        <v>85.06999999999999</v>
+      </c>
+      <c r="J194" s="8" t="n">
+        <v>10</v>
+      </c>
+      <c r="K194" s="10" t="n">
+        <v>8.51</v>
+      </c>
+      <c r="L194" s="23" t="n">
+        <v>8</v>
+      </c>
+      <c r="M194" s="8" t="inlineStr">
+        <is>
+          <t>DE</t>
+        </is>
+      </c>
+      <c r="N194" s="12" t="n">
+        <v>10</v>
+      </c>
+      <c r="O194" s="10" t="n"/>
+      <c r="P194" s="13" t="inlineStr">
+        <is>
+          <t>Ativo</t>
+        </is>
+      </c>
+      <c r="Q194" s="13" t="inlineStr">
+        <is>
+          <t>Adimplente</t>
+        </is>
+      </c>
+      <c r="R194" s="14" t="inlineStr"/>
+    </row>
+    <row r="195" ht="16" customHeight="1">
+      <c r="A195" s="15" t="inlineStr">
+        <is>
+          <t>LEONARDO VAZ DE FREITAS</t>
+        </is>
+      </c>
+      <c r="B195" s="16" t="n">
+        <v>1689.84</v>
+      </c>
+      <c r="C195" s="17" t="inlineStr">
+        <is>
+          <t>SUHAI</t>
+        </is>
+      </c>
+      <c r="D195" s="17" t="inlineStr">
+        <is>
+          <t>TUCSON</t>
+        </is>
+      </c>
+      <c r="E195" s="18" t="n">
+        <v>25</v>
+      </c>
+      <c r="F195" s="19" t="n">
+        <v>422.46</v>
+      </c>
+      <c r="G195" s="19" t="n">
+        <v>109.84</v>
+      </c>
+      <c r="H195" s="19" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="I195" s="19" t="n">
+        <v>107.64</v>
+      </c>
+      <c r="J195" s="17" t="n">
+        <v>12</v>
+      </c>
+      <c r="K195" s="19" t="n">
+        <v>8.970000000000001</v>
+      </c>
+      <c r="L195" s="24" t="n">
+        <v>8</v>
+      </c>
+      <c r="M195" s="17" t="inlineStr">
+        <is>
+          <t>DE</t>
+        </is>
+      </c>
+      <c r="N195" s="21" t="n">
+        <v>12</v>
+      </c>
+      <c r="O195" s="19" t="n"/>
+      <c r="P195" s="13" t="inlineStr">
+        <is>
+          <t>Ativo</t>
+        </is>
+      </c>
+      <c r="Q195" s="13" t="inlineStr">
+        <is>
+          <t>Adimplente</t>
+        </is>
+      </c>
+      <c r="R195" s="22" t="inlineStr"/>
+    </row>
+    <row r="196" ht="16" customHeight="1">
+      <c r="A196" s="6" t="inlineStr">
+        <is>
+          <t>VALDISLEI XAVIER DO NASCIMENTO</t>
+        </is>
+      </c>
+      <c r="B196" s="7" t="n">
+        <v>4204.31</v>
+      </c>
+      <c r="C196" s="8" t="inlineStr">
+        <is>
+          <t>BRADESCO</t>
+        </is>
+      </c>
+      <c r="D196" s="8" t="inlineStr">
+        <is>
+          <t>COROLLA</t>
+        </is>
+      </c>
+      <c r="E196" s="9" t="n">
+        <v>20</v>
+      </c>
+      <c r="F196" s="10" t="n">
+        <v>840.86</v>
+      </c>
+      <c r="G196" s="10" t="n">
+        <v>218.62</v>
+      </c>
+      <c r="H196" s="10" t="n">
+        <v>4.37</v>
+      </c>
+      <c r="I196" s="10" t="n">
+        <v>214.25</v>
+      </c>
+      <c r="J196" s="8" t="n">
+        <v>10</v>
+      </c>
+      <c r="K196" s="10" t="n">
+        <v>21.43</v>
+      </c>
+      <c r="L196" s="23" t="n">
+        <v>7</v>
+      </c>
+      <c r="M196" s="8" t="inlineStr">
+        <is>
+          <t>DE</t>
+        </is>
+      </c>
+      <c r="N196" s="12" t="n">
+        <v>10</v>
+      </c>
+      <c r="O196" s="10" t="n"/>
+      <c r="P196" s="13" t="inlineStr">
+        <is>
+          <t>Ativo</t>
+        </is>
+      </c>
+      <c r="Q196" s="13" t="inlineStr">
+        <is>
+          <t>Adimplente</t>
+        </is>
+      </c>
+      <c r="R196" s="14" t="inlineStr"/>
+    </row>
+    <row r="197" ht="16" customHeight="1">
+      <c r="A197" s="15" t="inlineStr">
+        <is>
+          <t>IVO REIS DO NASCIMENTO</t>
+        </is>
+      </c>
+      <c r="B197" s="16" t="n">
+        <v>1199.51</v>
+      </c>
+      <c r="C197" s="17" t="inlineStr">
+        <is>
+          <t>AZUL</t>
+        </is>
+      </c>
+      <c r="D197" s="17" t="inlineStr">
+        <is>
+          <t>CITY SEDAN</t>
+        </is>
+      </c>
+      <c r="E197" s="18" t="n">
+        <v>20</v>
+      </c>
+      <c r="F197" s="19" t="n">
+        <v>239.9</v>
+      </c>
+      <c r="G197" s="19" t="n">
+        <v>62.37</v>
+      </c>
+      <c r="H197" s="19" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="I197" s="19" t="n">
+        <v>61.13</v>
+      </c>
+      <c r="J197" s="17" t="n">
+        <v>1</v>
+      </c>
+      <c r="K197" s="19" t="n">
+        <v>61.13</v>
+      </c>
+      <c r="L197" s="24" t="n">
+        <v>7</v>
+      </c>
+      <c r="M197" s="17" t="inlineStr">
+        <is>
+          <t>DE</t>
+        </is>
+      </c>
+      <c r="N197" s="21" t="n">
+        <v>1</v>
+      </c>
+      <c r="O197" s="19" t="n"/>
+      <c r="P197" s="13" t="inlineStr">
+        <is>
+          <t>Ativo</t>
+        </is>
+      </c>
+      <c r="Q197" s="13" t="inlineStr">
+        <is>
+          <t>Adimplente</t>
+        </is>
+      </c>
+      <c r="R197" s="22" t="inlineStr"/>
+    </row>
+    <row r="198" ht="16" customHeight="1">
+      <c r="A198" s="6" t="inlineStr">
+        <is>
+          <t>ANDREA NASCIMENTO SANTANA MARTIENA</t>
+        </is>
+      </c>
+      <c r="B198" s="7" t="n">
+        <v>1986.95</v>
+      </c>
+      <c r="C198" s="8" t="inlineStr">
+        <is>
+          <t>TOKIO MARINE</t>
+        </is>
+      </c>
+      <c r="D198" s="8" t="inlineStr">
+        <is>
+          <t>CRETA</t>
+        </is>
+      </c>
+      <c r="E198" s="9" t="n">
+        <v>20</v>
+      </c>
+      <c r="F198" s="10" t="n">
+        <v>397.39</v>
+      </c>
+      <c r="G198" s="10" t="n">
+        <v>103.32</v>
+      </c>
+      <c r="H198" s="10" t="n">
+        <v>2.07</v>
+      </c>
+      <c r="I198" s="10" t="n">
+        <v>101.25</v>
+      </c>
+      <c r="J198" s="8" t="n">
+        <v>12</v>
+      </c>
+      <c r="K198" s="10" t="n">
+        <v>8.44</v>
+      </c>
+      <c r="L198" s="23" t="n">
+        <v>7</v>
+      </c>
+      <c r="M198" s="8" t="inlineStr">
+        <is>
+          <t>DE</t>
+        </is>
+      </c>
+      <c r="N198" s="12" t="n">
+        <v>12</v>
+      </c>
+      <c r="O198" s="10" t="n"/>
+      <c r="P198" s="13" t="inlineStr">
+        <is>
+          <t>Ativo</t>
+        </is>
+      </c>
+      <c r="Q198" s="13" t="inlineStr">
+        <is>
+          <t>Adimplente</t>
+        </is>
+      </c>
+      <c r="R198" s="14" t="inlineStr"/>
+    </row>
+    <row r="199" ht="16" customHeight="1">
+      <c r="A199" s="15" t="inlineStr">
+        <is>
+          <t>CAIO CESAR DOS SANTOS</t>
+        </is>
+      </c>
+      <c r="B199" s="16" t="n">
+        <v>3310.55</v>
+      </c>
+      <c r="C199" s="17" t="inlineStr">
+        <is>
+          <t>SUHAI</t>
+        </is>
+      </c>
+      <c r="D199" s="17" t="inlineStr">
+        <is>
+          <t>SIENA</t>
+        </is>
+      </c>
+      <c r="E199" s="18" t="n">
+        <v>20</v>
+      </c>
+      <c r="F199" s="19" t="n">
+        <v>662.11</v>
+      </c>
+      <c r="G199" s="19" t="n">
+        <v>172.15</v>
+      </c>
+      <c r="H199" s="19" t="n">
+        <v>3.44</v>
+      </c>
+      <c r="I199" s="19" t="n">
+        <v>168.71</v>
+      </c>
+      <c r="J199" s="17" t="n">
+        <v>12</v>
+      </c>
+      <c r="K199" s="19" t="n">
+        <v>14.06</v>
+      </c>
+      <c r="L199" s="24" t="n">
+        <v>6</v>
+      </c>
+      <c r="M199" s="17" t="inlineStr">
+        <is>
+          <t>DE</t>
+        </is>
+      </c>
+      <c r="N199" s="21" t="n">
+        <v>12</v>
+      </c>
+      <c r="O199" s="19" t="n"/>
+      <c r="P199" s="13" t="inlineStr">
+        <is>
+          <t>Ativo</t>
+        </is>
+      </c>
+      <c r="Q199" s="13" t="inlineStr">
+        <is>
+          <t>Adimplente</t>
+        </is>
+      </c>
+      <c r="R199" s="22" t="inlineStr"/>
+    </row>
+    <row r="200" ht="16" customHeight="1">
+      <c r="A200" s="6" t="inlineStr">
+        <is>
+          <t>IVO REIS DO NASCIMENTO</t>
+        </is>
+      </c>
+      <c r="B200" s="7" t="n">
+        <v>2141.74</v>
+      </c>
+      <c r="C200" s="8" t="inlineStr">
+        <is>
+          <t>MITSUI</t>
+        </is>
+      </c>
+      <c r="D200" s="8" t="inlineStr">
+        <is>
+          <t>FOX</t>
+        </is>
+      </c>
+      <c r="E200" s="9" t="n">
+        <v>20</v>
+      </c>
+      <c r="F200" s="10" t="n">
+        <v>428.35</v>
+      </c>
+      <c r="G200" s="10" t="n">
+        <v>111.37</v>
+      </c>
+      <c r="H200" s="10" t="n">
+        <v>2.23</v>
+      </c>
+      <c r="I200" s="10" t="n">
+        <v>109.14</v>
+      </c>
+      <c r="J200" s="8" t="n">
+        <v>10</v>
+      </c>
+      <c r="K200" s="10" t="n">
+        <v>10.91</v>
+      </c>
+      <c r="L200" s="23" t="n">
+        <v>6</v>
+      </c>
+      <c r="M200" s="8" t="inlineStr">
+        <is>
+          <t>DE</t>
+        </is>
+      </c>
+      <c r="N200" s="12" t="n">
+        <v>10</v>
+      </c>
+      <c r="O200" s="10" t="n"/>
+      <c r="P200" s="13" t="inlineStr">
+        <is>
+          <t>Ativo</t>
+        </is>
+      </c>
+      <c r="Q200" s="13" t="inlineStr">
+        <is>
+          <t>Adimplente</t>
+        </is>
+      </c>
+      <c r="R200" s="14" t="inlineStr"/>
+    </row>
+    <row r="201" ht="16" customHeight="1">
+      <c r="A201" s="15" t="inlineStr">
+        <is>
+          <t>LEIDE DAYANE DE SOUZA</t>
+        </is>
+      </c>
+      <c r="B201" s="16" t="n">
+        <v>1642.98</v>
+      </c>
+      <c r="C201" s="17" t="inlineStr">
+        <is>
+          <t>ALIRO</t>
+        </is>
+      </c>
+      <c r="D201" s="17" t="inlineStr">
+        <is>
+          <t>ECOSPORT</t>
+        </is>
+      </c>
+      <c r="E201" s="18" t="n">
+        <v>20</v>
+      </c>
+      <c r="F201" s="19" t="n">
+        <v>328.6</v>
+      </c>
+      <c r="G201" s="19" t="n">
+        <v>85.43000000000001</v>
+      </c>
+      <c r="H201" s="19" t="n">
+        <v>1.71</v>
+      </c>
+      <c r="I201" s="19" t="n">
+        <v>83.73</v>
+      </c>
+      <c r="J201" s="17" t="n">
+        <v>10</v>
+      </c>
+      <c r="K201" s="19" t="n">
+        <v>8.369999999999999</v>
+      </c>
+      <c r="L201" s="24" t="n">
+        <v>6</v>
+      </c>
+      <c r="M201" s="17" t="inlineStr">
+        <is>
+          <t>DE</t>
+        </is>
+      </c>
+      <c r="N201" s="21" t="n">
+        <v>10</v>
+      </c>
+      <c r="O201" s="19" t="n"/>
+      <c r="P201" s="13" t="inlineStr">
+        <is>
+          <t>Ativo</t>
+        </is>
+      </c>
+      <c r="Q201" s="13" t="inlineStr">
+        <is>
+          <t>Adimplente</t>
+        </is>
+      </c>
+      <c r="R201" s="22" t="inlineStr"/>
+    </row>
+    <row r="202" ht="18" customHeight="1">
+      <c r="A202" s="25" t="inlineStr">
+        <is>
+          <t>TOTAL  JAN/26</t>
+        </is>
+      </c>
+      <c r="K202" s="26" t="n">
+        <v>258.82</v>
+      </c>
+      <c r="L202" s="27" t="n"/>
+      <c r="M202" s="27" t="n"/>
+      <c r="N202" s="27" t="n"/>
+      <c r="O202" s="27" t="n"/>
+      <c r="P202" s="27" t="n"/>
+      <c r="Q202" s="27" t="n"/>
+      <c r="R202" s="27" t="n"/>
+    </row>
+    <row r="204" ht="22" customHeight="1">
+      <c r="A204" s="3" t="inlineStr">
         <is>
           <t>fev/26</t>
         </is>
       </c>
-      <c r="B142" s="4" t="inlineStr">
+      <c r="B204" s="4" t="inlineStr">
         <is>
           <t>PRÊMIO LÍQ</t>
         </is>
       </c>
-      <c r="C142" s="4" t="inlineStr">
+      <c r="C204" s="4" t="inlineStr">
         <is>
           <t>SEGURADORA</t>
         </is>
       </c>
-      <c r="D142" s="4" t="inlineStr">
+      <c r="D204" s="4" t="inlineStr">
         <is>
           <t>ITEM</t>
         </is>
       </c>
-      <c r="E142" s="4" t="inlineStr">
+      <c r="E204" s="4" t="inlineStr">
         <is>
           <t>COM%</t>
         </is>
       </c>
-      <c r="F142" s="4" t="inlineStr">
+      <c r="F204" s="4" t="inlineStr">
         <is>
           <t>COMISSÃO</t>
         </is>
       </c>
-      <c r="G142" s="4" t="inlineStr">
+      <c r="G204" s="4" t="inlineStr">
         <is>
           <t>26%</t>
         </is>
       </c>
-      <c r="H142" s="4" t="inlineStr">
+      <c r="H204" s="4" t="inlineStr">
         <is>
           <t>2% DA</t>
         </is>
       </c>
-      <c r="I142" s="4" t="inlineStr">
+      <c r="I204" s="4" t="inlineStr">
         <is>
           <t>RECEBIDO</t>
         </is>
       </c>
-      <c r="J142" s="4" t="inlineStr">
+      <c r="J204" s="4" t="inlineStr">
         <is>
           <t>VEZES</t>
         </is>
       </c>
-      <c r="K142" s="4" t="inlineStr">
+      <c r="K204" s="4" t="inlineStr">
         <is>
           <t>RECEBER</t>
         </is>
       </c>
-      <c r="L142" s="5" t="inlineStr"/>
-      <c r="M142" s="4" t="inlineStr">
-        <is>
-          <t>DE</t>
-        </is>
-      </c>
-      <c r="N142" s="5" t="inlineStr"/>
-      <c r="O142" s="4" t="inlineStr">
+      <c r="L204" s="5" t="inlineStr"/>
+      <c r="M204" s="4" t="inlineStr">
+        <is>
+          <t>DE</t>
+        </is>
+      </c>
+      <c r="N204" s="5" t="inlineStr"/>
+      <c r="O204" s="4" t="inlineStr">
         <is>
           <t>AJUSTE</t>
         </is>
       </c>
-      <c r="P142" s="4" t="inlineStr">
+      <c r="P204" s="4" t="inlineStr">
         <is>
           <t>STATUS</t>
         </is>
       </c>
-      <c r="Q142" s="4" t="inlineStr">
+      <c r="Q204" s="4" t="inlineStr">
         <is>
           <t>ADIMPLÊNCIA</t>
         </is>
       </c>
-      <c r="R142" s="4" t="inlineStr">
+      <c r="R204" s="4" t="inlineStr">
         <is>
           <t>OBS</t>
         </is>
       </c>
     </row>
-    <row r="143" ht="16" customHeight="1">
-      <c r="A143" s="28" t="inlineStr">
-        <is>
-          <t>⚠  Dados de fev/26 ainda não inseridos — preencher manualmente</t>
-        </is>
-      </c>
-    </row>
-    <row r="145" ht="22" customHeight="1">
-      <c r="A145" s="3" t="inlineStr">
+    <row r="205" ht="16" customHeight="1">
+      <c r="A205" s="6" t="inlineStr">
+        <is>
+          <t>SOLANGE SILVA DE JESUS</t>
+        </is>
+      </c>
+      <c r="B205" s="7" t="n">
+        <v>1602.96</v>
+      </c>
+      <c r="C205" s="8" t="inlineStr">
+        <is>
+          <t>TOKIO MARINE</t>
+        </is>
+      </c>
+      <c r="D205" s="8" t="inlineStr">
+        <is>
+          <t>I30</t>
+        </is>
+      </c>
+      <c r="E205" s="9" t="n">
+        <v>20</v>
+      </c>
+      <c r="F205" s="10" t="n">
+        <v>320.59</v>
+      </c>
+      <c r="G205" s="10" t="n">
+        <v>83.34999999999999</v>
+      </c>
+      <c r="H205" s="10" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="I205" s="10" t="n">
+        <v>81.69</v>
+      </c>
+      <c r="J205" s="8" t="n">
+        <v>12</v>
+      </c>
+      <c r="K205" s="10" t="n">
+        <v>6.81</v>
+      </c>
+      <c r="L205" s="23" t="n">
+        <v>11</v>
+      </c>
+      <c r="M205" s="8" t="inlineStr">
+        <is>
+          <t>DE</t>
+        </is>
+      </c>
+      <c r="N205" s="12" t="n">
+        <v>12</v>
+      </c>
+      <c r="O205" s="10" t="n"/>
+      <c r="P205" s="13" t="inlineStr">
+        <is>
+          <t>Ativo</t>
+        </is>
+      </c>
+      <c r="Q205" s="13" t="inlineStr">
+        <is>
+          <t>Adimplente</t>
+        </is>
+      </c>
+      <c r="R205" s="14" t="inlineStr"/>
+    </row>
+    <row r="206" ht="16" customHeight="1">
+      <c r="A206" s="15" t="inlineStr">
+        <is>
+          <t>ROSANGELA DE JESUS MELO</t>
+        </is>
+      </c>
+      <c r="B206" s="16" t="n">
+        <v>1454.42</v>
+      </c>
+      <c r="C206" s="17" t="inlineStr">
+        <is>
+          <t>SUHAI</t>
+        </is>
+      </c>
+      <c r="D206" s="17" t="inlineStr">
+        <is>
+          <t>IDEA</t>
+        </is>
+      </c>
+      <c r="E206" s="18" t="n">
+        <v>25</v>
+      </c>
+      <c r="F206" s="19" t="n">
+        <v>363.61</v>
+      </c>
+      <c r="G206" s="19" t="n">
+        <v>94.54000000000001</v>
+      </c>
+      <c r="H206" s="19" t="n">
+        <v>1.89</v>
+      </c>
+      <c r="I206" s="19" t="n">
+        <v>92.65000000000001</v>
+      </c>
+      <c r="J206" s="17" t="n">
+        <v>1</v>
+      </c>
+      <c r="K206" s="19" t="n">
+        <v>92.65000000000001</v>
+      </c>
+      <c r="L206" s="24" t="n">
+        <v>9</v>
+      </c>
+      <c r="M206" s="17" t="inlineStr">
+        <is>
+          <t>DE</t>
+        </is>
+      </c>
+      <c r="N206" s="21" t="n">
+        <v>1</v>
+      </c>
+      <c r="O206" s="19" t="n"/>
+      <c r="P206" s="13" t="inlineStr">
+        <is>
+          <t>Ativo</t>
+        </is>
+      </c>
+      <c r="Q206" s="13" t="inlineStr">
+        <is>
+          <t>Adimplente</t>
+        </is>
+      </c>
+      <c r="R206" s="22" t="inlineStr"/>
+    </row>
+    <row r="207" ht="16" customHeight="1">
+      <c r="A207" s="6" t="inlineStr">
+        <is>
+          <t>ANTONIO CARLOS DOS SANTOS</t>
+        </is>
+      </c>
+      <c r="B207" s="7" t="n">
+        <v>2201.31</v>
+      </c>
+      <c r="C207" s="8" t="inlineStr">
+        <is>
+          <t>PORTO</t>
+        </is>
+      </c>
+      <c r="D207" s="8" t="inlineStr">
+        <is>
+          <t>TUCSON</t>
+        </is>
+      </c>
+      <c r="E207" s="9" t="n">
+        <v>18</v>
+      </c>
+      <c r="F207" s="10" t="n">
+        <v>396.24</v>
+      </c>
+      <c r="G207" s="10" t="n">
+        <v>103.02</v>
+      </c>
+      <c r="H207" s="10" t="n">
+        <v>2.06</v>
+      </c>
+      <c r="I207" s="10" t="n">
+        <v>100.96</v>
+      </c>
+      <c r="J207" s="8" t="n">
+        <v>10</v>
+      </c>
+      <c r="K207" s="10" t="n">
+        <v>10.1</v>
+      </c>
+      <c r="L207" s="23" t="n">
+        <v>9</v>
+      </c>
+      <c r="M207" s="8" t="inlineStr">
+        <is>
+          <t>DE</t>
+        </is>
+      </c>
+      <c r="N207" s="12" t="n">
+        <v>10</v>
+      </c>
+      <c r="O207" s="10" t="n"/>
+      <c r="P207" s="13" t="inlineStr">
+        <is>
+          <t>Ativo</t>
+        </is>
+      </c>
+      <c r="Q207" s="13" t="inlineStr">
+        <is>
+          <t>Adimplente</t>
+        </is>
+      </c>
+      <c r="R207" s="14" t="inlineStr"/>
+    </row>
+    <row r="208" ht="16" customHeight="1">
+      <c r="A208" s="15" t="inlineStr">
+        <is>
+          <t>OTAVIANO DE JESUS</t>
+        </is>
+      </c>
+      <c r="B208" s="16" t="n">
+        <v>1854.88</v>
+      </c>
+      <c r="C208" s="17" t="inlineStr">
+        <is>
+          <t>PORTO</t>
+        </is>
+      </c>
+      <c r="D208" s="17" t="inlineStr">
+        <is>
+          <t>CORSA</t>
+        </is>
+      </c>
+      <c r="E208" s="18" t="n">
+        <v>18</v>
+      </c>
+      <c r="F208" s="19" t="n">
+        <v>333.88</v>
+      </c>
+      <c r="G208" s="19" t="n">
+        <v>86.81</v>
+      </c>
+      <c r="H208" s="19" t="n">
+        <v>1.74</v>
+      </c>
+      <c r="I208" s="19" t="n">
+        <v>85.06999999999999</v>
+      </c>
+      <c r="J208" s="17" t="n">
+        <v>10</v>
+      </c>
+      <c r="K208" s="19" t="n">
+        <v>8.51</v>
+      </c>
+      <c r="L208" s="24" t="n">
+        <v>9</v>
+      </c>
+      <c r="M208" s="17" t="inlineStr">
+        <is>
+          <t>DE</t>
+        </is>
+      </c>
+      <c r="N208" s="21" t="n">
+        <v>10</v>
+      </c>
+      <c r="O208" s="19" t="n"/>
+      <c r="P208" s="13" t="inlineStr">
+        <is>
+          <t>Ativo</t>
+        </is>
+      </c>
+      <c r="Q208" s="13" t="inlineStr">
+        <is>
+          <t>Adimplente</t>
+        </is>
+      </c>
+      <c r="R208" s="22" t="inlineStr"/>
+    </row>
+    <row r="209" ht="16" customHeight="1">
+      <c r="A209" s="6" t="inlineStr">
+        <is>
+          <t>LEONARDO VAZ DE FREITAS</t>
+        </is>
+      </c>
+      <c r="B209" s="7" t="n">
+        <v>1689.84</v>
+      </c>
+      <c r="C209" s="8" t="inlineStr">
+        <is>
+          <t>SUHAI</t>
+        </is>
+      </c>
+      <c r="D209" s="8" t="inlineStr">
+        <is>
+          <t>TUCSON</t>
+        </is>
+      </c>
+      <c r="E209" s="9" t="n">
+        <v>25</v>
+      </c>
+      <c r="F209" s="10" t="n">
+        <v>422.46</v>
+      </c>
+      <c r="G209" s="10" t="n">
+        <v>109.84</v>
+      </c>
+      <c r="H209" s="10" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="I209" s="10" t="n">
+        <v>107.64</v>
+      </c>
+      <c r="J209" s="8" t="n">
+        <v>12</v>
+      </c>
+      <c r="K209" s="10" t="n">
+        <v>8.970000000000001</v>
+      </c>
+      <c r="L209" s="23" t="n">
+        <v>9</v>
+      </c>
+      <c r="M209" s="8" t="inlineStr">
+        <is>
+          <t>DE</t>
+        </is>
+      </c>
+      <c r="N209" s="12" t="n">
+        <v>12</v>
+      </c>
+      <c r="O209" s="10" t="n"/>
+      <c r="P209" s="13" t="inlineStr">
+        <is>
+          <t>Ativo</t>
+        </is>
+      </c>
+      <c r="Q209" s="13" t="inlineStr">
+        <is>
+          <t>Adimplente</t>
+        </is>
+      </c>
+      <c r="R209" s="14" t="inlineStr"/>
+    </row>
+    <row r="210" ht="16" customHeight="1">
+      <c r="A210" s="15" t="inlineStr">
+        <is>
+          <t>VALDISLEI XAVIER DO NASCIMENTO</t>
+        </is>
+      </c>
+      <c r="B210" s="16" t="n">
+        <v>4204.31</v>
+      </c>
+      <c r="C210" s="17" t="inlineStr">
+        <is>
+          <t>BRADESCO</t>
+        </is>
+      </c>
+      <c r="D210" s="17" t="inlineStr">
+        <is>
+          <t>COROLLA</t>
+        </is>
+      </c>
+      <c r="E210" s="18" t="n">
+        <v>20</v>
+      </c>
+      <c r="F210" s="19" t="n">
+        <v>840.86</v>
+      </c>
+      <c r="G210" s="19" t="n">
+        <v>218.62</v>
+      </c>
+      <c r="H210" s="19" t="n">
+        <v>4.37</v>
+      </c>
+      <c r="I210" s="19" t="n">
+        <v>214.25</v>
+      </c>
+      <c r="J210" s="17" t="n">
+        <v>10</v>
+      </c>
+      <c r="K210" s="19" t="n">
+        <v>21.43</v>
+      </c>
+      <c r="L210" s="24" t="n">
+        <v>8</v>
+      </c>
+      <c r="M210" s="17" t="inlineStr">
+        <is>
+          <t>DE</t>
+        </is>
+      </c>
+      <c r="N210" s="21" t="n">
+        <v>10</v>
+      </c>
+      <c r="O210" s="19" t="n"/>
+      <c r="P210" s="13" t="inlineStr">
+        <is>
+          <t>Ativo</t>
+        </is>
+      </c>
+      <c r="Q210" s="13" t="inlineStr">
+        <is>
+          <t>Adimplente</t>
+        </is>
+      </c>
+      <c r="R210" s="22" t="inlineStr"/>
+    </row>
+    <row r="211" ht="16" customHeight="1">
+      <c r="A211" s="6" t="inlineStr">
+        <is>
+          <t>IVO REIS DO NASCIMENTO</t>
+        </is>
+      </c>
+      <c r="B211" s="7" t="n">
+        <v>1199.51</v>
+      </c>
+      <c r="C211" s="8" t="inlineStr">
+        <is>
+          <t>AZUL</t>
+        </is>
+      </c>
+      <c r="D211" s="8" t="inlineStr">
+        <is>
+          <t>CITY SEDAN</t>
+        </is>
+      </c>
+      <c r="E211" s="9" t="n">
+        <v>20</v>
+      </c>
+      <c r="F211" s="10" t="n">
+        <v>239.9</v>
+      </c>
+      <c r="G211" s="10" t="n">
+        <v>62.37</v>
+      </c>
+      <c r="H211" s="10" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="I211" s="10" t="n">
+        <v>61.13</v>
+      </c>
+      <c r="J211" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="K211" s="10" t="n">
+        <v>61.13</v>
+      </c>
+      <c r="L211" s="23" t="n">
+        <v>8</v>
+      </c>
+      <c r="M211" s="8" t="inlineStr">
+        <is>
+          <t>DE</t>
+        </is>
+      </c>
+      <c r="N211" s="12" t="n">
+        <v>1</v>
+      </c>
+      <c r="O211" s="10" t="n"/>
+      <c r="P211" s="13" t="inlineStr">
+        <is>
+          <t>Ativo</t>
+        </is>
+      </c>
+      <c r="Q211" s="13" t="inlineStr">
+        <is>
+          <t>Adimplente</t>
+        </is>
+      </c>
+      <c r="R211" s="14" t="inlineStr"/>
+    </row>
+    <row r="212" ht="16" customHeight="1">
+      <c r="A212" s="15" t="inlineStr">
+        <is>
+          <t>ANDREA NASCIMENTO SANTANA MARTIENA</t>
+        </is>
+      </c>
+      <c r="B212" s="16" t="n">
+        <v>1986.95</v>
+      </c>
+      <c r="C212" s="17" t="inlineStr">
+        <is>
+          <t>TOKIO MARINE</t>
+        </is>
+      </c>
+      <c r="D212" s="17" t="inlineStr">
+        <is>
+          <t>CRETA</t>
+        </is>
+      </c>
+      <c r="E212" s="18" t="n">
+        <v>20</v>
+      </c>
+      <c r="F212" s="19" t="n">
+        <v>397.39</v>
+      </c>
+      <c r="G212" s="19" t="n">
+        <v>103.32</v>
+      </c>
+      <c r="H212" s="19" t="n">
+        <v>2.07</v>
+      </c>
+      <c r="I212" s="19" t="n">
+        <v>101.25</v>
+      </c>
+      <c r="J212" s="17" t="n">
+        <v>12</v>
+      </c>
+      <c r="K212" s="19" t="n">
+        <v>8.44</v>
+      </c>
+      <c r="L212" s="24" t="n">
+        <v>8</v>
+      </c>
+      <c r="M212" s="17" t="inlineStr">
+        <is>
+          <t>DE</t>
+        </is>
+      </c>
+      <c r="N212" s="21" t="n">
+        <v>12</v>
+      </c>
+      <c r="O212" s="19" t="n"/>
+      <c r="P212" s="13" t="inlineStr">
+        <is>
+          <t>Ativo</t>
+        </is>
+      </c>
+      <c r="Q212" s="13" t="inlineStr">
+        <is>
+          <t>Adimplente</t>
+        </is>
+      </c>
+      <c r="R212" s="22" t="inlineStr"/>
+    </row>
+    <row r="213" ht="16" customHeight="1">
+      <c r="A213" s="6" t="inlineStr">
+        <is>
+          <t>CAIO CESAR DOS SANTOS</t>
+        </is>
+      </c>
+      <c r="B213" s="7" t="n">
+        <v>3310.55</v>
+      </c>
+      <c r="C213" s="8" t="inlineStr">
+        <is>
+          <t>SUHAI</t>
+        </is>
+      </c>
+      <c r="D213" s="8" t="inlineStr">
+        <is>
+          <t>SIENA</t>
+        </is>
+      </c>
+      <c r="E213" s="9" t="n">
+        <v>20</v>
+      </c>
+      <c r="F213" s="10" t="n">
+        <v>662.11</v>
+      </c>
+      <c r="G213" s="10" t="n">
+        <v>172.15</v>
+      </c>
+      <c r="H213" s="10" t="n">
+        <v>3.44</v>
+      </c>
+      <c r="I213" s="10" t="n">
+        <v>168.71</v>
+      </c>
+      <c r="J213" s="8" t="n">
+        <v>12</v>
+      </c>
+      <c r="K213" s="10" t="n">
+        <v>14.06</v>
+      </c>
+      <c r="L213" s="23" t="n">
+        <v>7</v>
+      </c>
+      <c r="M213" s="8" t="inlineStr">
+        <is>
+          <t>DE</t>
+        </is>
+      </c>
+      <c r="N213" s="12" t="n">
+        <v>12</v>
+      </c>
+      <c r="O213" s="10" t="n"/>
+      <c r="P213" s="13" t="inlineStr">
+        <is>
+          <t>Ativo</t>
+        </is>
+      </c>
+      <c r="Q213" s="13" t="inlineStr">
+        <is>
+          <t>Adimplente</t>
+        </is>
+      </c>
+      <c r="R213" s="14" t="inlineStr"/>
+    </row>
+    <row r="214" ht="16" customHeight="1">
+      <c r="A214" s="15" t="inlineStr">
+        <is>
+          <t>IVO REIS DO NASCIMENTO</t>
+        </is>
+      </c>
+      <c r="B214" s="16" t="n">
+        <v>2141.74</v>
+      </c>
+      <c r="C214" s="17" t="inlineStr">
+        <is>
+          <t>MITSUI</t>
+        </is>
+      </c>
+      <c r="D214" s="17" t="inlineStr">
+        <is>
+          <t>FOX</t>
+        </is>
+      </c>
+      <c r="E214" s="18" t="n">
+        <v>20</v>
+      </c>
+      <c r="F214" s="19" t="n">
+        <v>428.35</v>
+      </c>
+      <c r="G214" s="19" t="n">
+        <v>111.37</v>
+      </c>
+      <c r="H214" s="19" t="n">
+        <v>2.23</v>
+      </c>
+      <c r="I214" s="19" t="n">
+        <v>109.14</v>
+      </c>
+      <c r="J214" s="17" t="n">
+        <v>10</v>
+      </c>
+      <c r="K214" s="19" t="n">
+        <v>10.91</v>
+      </c>
+      <c r="L214" s="24" t="n">
+        <v>7</v>
+      </c>
+      <c r="M214" s="17" t="inlineStr">
+        <is>
+          <t>DE</t>
+        </is>
+      </c>
+      <c r="N214" s="21" t="n">
+        <v>10</v>
+      </c>
+      <c r="O214" s="19" t="n"/>
+      <c r="P214" s="13" t="inlineStr">
+        <is>
+          <t>Ativo</t>
+        </is>
+      </c>
+      <c r="Q214" s="13" t="inlineStr">
+        <is>
+          <t>Adimplente</t>
+        </is>
+      </c>
+      <c r="R214" s="22" t="inlineStr"/>
+    </row>
+    <row r="215" ht="16" customHeight="1">
+      <c r="A215" s="6" t="inlineStr">
+        <is>
+          <t>LEIDE DAYANE DE SOUZA</t>
+        </is>
+      </c>
+      <c r="B215" s="7" t="n">
+        <v>1642.98</v>
+      </c>
+      <c r="C215" s="8" t="inlineStr">
+        <is>
+          <t>ALIRO</t>
+        </is>
+      </c>
+      <c r="D215" s="8" t="inlineStr">
+        <is>
+          <t>ECOSPORT</t>
+        </is>
+      </c>
+      <c r="E215" s="9" t="n">
+        <v>20</v>
+      </c>
+      <c r="F215" s="10" t="n">
+        <v>328.6</v>
+      </c>
+      <c r="G215" s="10" t="n">
+        <v>85.43000000000001</v>
+      </c>
+      <c r="H215" s="10" t="n">
+        <v>1.71</v>
+      </c>
+      <c r="I215" s="10" t="n">
+        <v>83.73</v>
+      </c>
+      <c r="J215" s="8" t="n">
+        <v>10</v>
+      </c>
+      <c r="K215" s="10" t="n">
+        <v>8.369999999999999</v>
+      </c>
+      <c r="L215" s="23" t="n">
+        <v>7</v>
+      </c>
+      <c r="M215" s="8" t="inlineStr">
+        <is>
+          <t>DE</t>
+        </is>
+      </c>
+      <c r="N215" s="12" t="n">
+        <v>10</v>
+      </c>
+      <c r="O215" s="10" t="n"/>
+      <c r="P215" s="13" t="inlineStr">
+        <is>
+          <t>Ativo</t>
+        </is>
+      </c>
+      <c r="Q215" s="13" t="inlineStr">
+        <is>
+          <t>Adimplente</t>
+        </is>
+      </c>
+      <c r="R215" s="14" t="inlineStr"/>
+    </row>
+    <row r="216" ht="18" customHeight="1">
+      <c r="A216" s="25" t="inlineStr">
+        <is>
+          <t>TOTAL  FEV/26</t>
+        </is>
+      </c>
+      <c r="K216" s="26" t="n">
+        <v>251.38</v>
+      </c>
+      <c r="L216" s="27" t="n"/>
+      <c r="M216" s="27" t="n"/>
+      <c r="N216" s="27" t="n"/>
+      <c r="O216" s="27" t="n"/>
+      <c r="P216" s="27" t="n"/>
+      <c r="Q216" s="27" t="n"/>
+      <c r="R216" s="27" t="n"/>
+    </row>
+    <row r="218" ht="22" customHeight="1">
+      <c r="A218" s="3" t="inlineStr">
         <is>
           <t>mar/26</t>
         </is>
       </c>
-      <c r="B145" s="4" t="inlineStr">
+      <c r="B218" s="4" t="inlineStr">
         <is>
           <t>PRÊMIO LÍQ</t>
         </is>
       </c>
-      <c r="C145" s="4" t="inlineStr">
+      <c r="C218" s="4" t="inlineStr">
         <is>
           <t>SEGURADORA</t>
         </is>
       </c>
-      <c r="D145" s="4" t="inlineStr">
+      <c r="D218" s="4" t="inlineStr">
         <is>
           <t>ITEM</t>
         </is>
       </c>
-      <c r="E145" s="4" t="inlineStr">
+      <c r="E218" s="4" t="inlineStr">
         <is>
           <t>COM%</t>
         </is>
       </c>
-      <c r="F145" s="4" t="inlineStr">
+      <c r="F218" s="4" t="inlineStr">
         <is>
           <t>COMISSÃO</t>
         </is>
       </c>
-      <c r="G145" s="4" t="inlineStr">
+      <c r="G218" s="4" t="inlineStr">
         <is>
           <t>26%</t>
         </is>
       </c>
-      <c r="H145" s="4" t="inlineStr">
+      <c r="H218" s="4" t="inlineStr">
         <is>
           <t>2% DA</t>
         </is>
       </c>
-      <c r="I145" s="4" t="inlineStr">
+      <c r="I218" s="4" t="inlineStr">
         <is>
           <t>RECEBIDO</t>
         </is>
       </c>
-      <c r="J145" s="4" t="inlineStr">
+      <c r="J218" s="4" t="inlineStr">
         <is>
           <t>VEZES</t>
         </is>
       </c>
-      <c r="K145" s="4" t="inlineStr">
+      <c r="K218" s="4" t="inlineStr">
         <is>
           <t>RECEBER</t>
         </is>
       </c>
-      <c r="L145" s="5" t="inlineStr"/>
-      <c r="M145" s="4" t="inlineStr">
-        <is>
-          <t>DE</t>
-        </is>
-      </c>
-      <c r="N145" s="5" t="inlineStr"/>
-      <c r="O145" s="4" t="inlineStr">
+      <c r="L218" s="5" t="inlineStr"/>
+      <c r="M218" s="4" t="inlineStr">
+        <is>
+          <t>DE</t>
+        </is>
+      </c>
+      <c r="N218" s="5" t="inlineStr"/>
+      <c r="O218" s="4" t="inlineStr">
         <is>
           <t>AJUSTE</t>
         </is>
       </c>
-      <c r="P145" s="4" t="inlineStr">
+      <c r="P218" s="4" t="inlineStr">
         <is>
           <t>STATUS</t>
         </is>
       </c>
-      <c r="Q145" s="4" t="inlineStr">
+      <c r="Q218" s="4" t="inlineStr">
         <is>
           <t>ADIMPLÊNCIA</t>
         </is>
       </c>
-      <c r="R145" s="4" t="inlineStr">
+      <c r="R218" s="4" t="inlineStr">
         <is>
           <t>OBS</t>
         </is>
       </c>
     </row>
-    <row r="146" ht="16" customHeight="1">
-      <c r="A146" s="28" t="inlineStr">
-        <is>
-          <t>⚠  Dados de mar/26 ainda não inseridos — preencher manualmente</t>
-        </is>
-      </c>
-    </row>
-    <row r="148" ht="22" customHeight="1">
-      <c r="A148" s="3" t="inlineStr">
+    <row r="219" ht="16" customHeight="1">
+      <c r="A219" s="6" t="inlineStr">
+        <is>
+          <t>SOLANGE SILVA DE JESUS</t>
+        </is>
+      </c>
+      <c r="B219" s="7" t="n">
+        <v>1602.96</v>
+      </c>
+      <c r="C219" s="8" t="inlineStr">
+        <is>
+          <t>TOKIO MARINE</t>
+        </is>
+      </c>
+      <c r="D219" s="8" t="inlineStr">
+        <is>
+          <t>I30</t>
+        </is>
+      </c>
+      <c r="E219" s="9" t="n">
+        <v>20</v>
+      </c>
+      <c r="F219" s="10" t="n">
+        <v>320.59</v>
+      </c>
+      <c r="G219" s="10" t="n">
+        <v>83.34999999999999</v>
+      </c>
+      <c r="H219" s="10" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="I219" s="10" t="n">
+        <v>81.69</v>
+      </c>
+      <c r="J219" s="8" t="n">
+        <v>12</v>
+      </c>
+      <c r="K219" s="10" t="n">
+        <v>6.81</v>
+      </c>
+      <c r="L219" s="11" t="n">
+        <v>12</v>
+      </c>
+      <c r="M219" s="8" t="inlineStr">
+        <is>
+          <t>DE</t>
+        </is>
+      </c>
+      <c r="N219" s="12" t="n">
+        <v>12</v>
+      </c>
+      <c r="O219" s="10" t="n"/>
+      <c r="P219" s="13" t="inlineStr">
+        <is>
+          <t>Ativo</t>
+        </is>
+      </c>
+      <c r="Q219" s="13" t="inlineStr">
+        <is>
+          <t>Adimplente</t>
+        </is>
+      </c>
+      <c r="R219" s="14" t="inlineStr"/>
+    </row>
+    <row r="220" ht="16" customHeight="1">
+      <c r="A220" s="15" t="inlineStr">
+        <is>
+          <t>ROSANGELA DE JESUS MELO</t>
+        </is>
+      </c>
+      <c r="B220" s="16" t="n">
+        <v>1454.42</v>
+      </c>
+      <c r="C220" s="17" t="inlineStr">
+        <is>
+          <t>SUHAI</t>
+        </is>
+      </c>
+      <c r="D220" s="17" t="inlineStr">
+        <is>
+          <t>IDEA</t>
+        </is>
+      </c>
+      <c r="E220" s="18" t="n">
+        <v>25</v>
+      </c>
+      <c r="F220" s="19" t="n">
+        <v>363.61</v>
+      </c>
+      <c r="G220" s="19" t="n">
+        <v>94.54000000000001</v>
+      </c>
+      <c r="H220" s="19" t="n">
+        <v>1.89</v>
+      </c>
+      <c r="I220" s="19" t="n">
+        <v>92.65000000000001</v>
+      </c>
+      <c r="J220" s="17" t="n">
+        <v>1</v>
+      </c>
+      <c r="K220" s="19" t="n">
+        <v>92.65000000000001</v>
+      </c>
+      <c r="L220" s="24" t="n">
+        <v>10</v>
+      </c>
+      <c r="M220" s="17" t="inlineStr">
+        <is>
+          <t>DE</t>
+        </is>
+      </c>
+      <c r="N220" s="21" t="n">
+        <v>1</v>
+      </c>
+      <c r="O220" s="19" t="n"/>
+      <c r="P220" s="13" t="inlineStr">
+        <is>
+          <t>Ativo</t>
+        </is>
+      </c>
+      <c r="Q220" s="13" t="inlineStr">
+        <is>
+          <t>Adimplente</t>
+        </is>
+      </c>
+      <c r="R220" s="22" t="inlineStr"/>
+    </row>
+    <row r="221" ht="16" customHeight="1">
+      <c r="A221" s="6" t="inlineStr">
+        <is>
+          <t>ANTONIO CARLOS DOS SANTOS</t>
+        </is>
+      </c>
+      <c r="B221" s="7" t="n">
+        <v>2201.31</v>
+      </c>
+      <c r="C221" s="8" t="inlineStr">
+        <is>
+          <t>PORTO</t>
+        </is>
+      </c>
+      <c r="D221" s="8" t="inlineStr">
+        <is>
+          <t>TUCSON</t>
+        </is>
+      </c>
+      <c r="E221" s="9" t="n">
+        <v>18</v>
+      </c>
+      <c r="F221" s="10" t="n">
+        <v>396.24</v>
+      </c>
+      <c r="G221" s="10" t="n">
+        <v>103.02</v>
+      </c>
+      <c r="H221" s="10" t="n">
+        <v>2.06</v>
+      </c>
+      <c r="I221" s="10" t="n">
+        <v>100.96</v>
+      </c>
+      <c r="J221" s="8" t="n">
+        <v>10</v>
+      </c>
+      <c r="K221" s="10" t="n">
+        <v>10.1</v>
+      </c>
+      <c r="L221" s="11" t="n">
+        <v>10</v>
+      </c>
+      <c r="M221" s="8" t="inlineStr">
+        <is>
+          <t>DE</t>
+        </is>
+      </c>
+      <c r="N221" s="12" t="n">
+        <v>10</v>
+      </c>
+      <c r="O221" s="10" t="n"/>
+      <c r="P221" s="13" t="inlineStr">
+        <is>
+          <t>Ativo</t>
+        </is>
+      </c>
+      <c r="Q221" s="13" t="inlineStr">
+        <is>
+          <t>Adimplente</t>
+        </is>
+      </c>
+      <c r="R221" s="14" t="inlineStr"/>
+    </row>
+    <row r="222" ht="16" customHeight="1">
+      <c r="A222" s="15" t="inlineStr">
+        <is>
+          <t>OTAVIANO DE JESUS</t>
+        </is>
+      </c>
+      <c r="B222" s="16" t="n">
+        <v>1854.88</v>
+      </c>
+      <c r="C222" s="17" t="inlineStr">
+        <is>
+          <t>PORTO</t>
+        </is>
+      </c>
+      <c r="D222" s="17" t="inlineStr">
+        <is>
+          <t>CORSA</t>
+        </is>
+      </c>
+      <c r="E222" s="18" t="n">
+        <v>18</v>
+      </c>
+      <c r="F222" s="19" t="n">
+        <v>333.88</v>
+      </c>
+      <c r="G222" s="19" t="n">
+        <v>86.81</v>
+      </c>
+      <c r="H222" s="19" t="n">
+        <v>1.74</v>
+      </c>
+      <c r="I222" s="19" t="n">
+        <v>85.06999999999999</v>
+      </c>
+      <c r="J222" s="17" t="n">
+        <v>10</v>
+      </c>
+      <c r="K222" s="19" t="n">
+        <v>8.51</v>
+      </c>
+      <c r="L222" s="20" t="n">
+        <v>10</v>
+      </c>
+      <c r="M222" s="17" t="inlineStr">
+        <is>
+          <t>DE</t>
+        </is>
+      </c>
+      <c r="N222" s="21" t="n">
+        <v>10</v>
+      </c>
+      <c r="O222" s="19" t="n"/>
+      <c r="P222" s="13" t="inlineStr">
+        <is>
+          <t>Ativo</t>
+        </is>
+      </c>
+      <c r="Q222" s="13" t="inlineStr">
+        <is>
+          <t>Adimplente</t>
+        </is>
+      </c>
+      <c r="R222" s="22" t="inlineStr"/>
+    </row>
+    <row r="223" ht="16" customHeight="1">
+      <c r="A223" s="6" t="inlineStr">
+        <is>
+          <t>LEONARDO VAZ DE FREITAS</t>
+        </is>
+      </c>
+      <c r="B223" s="7" t="n">
+        <v>1689.84</v>
+      </c>
+      <c r="C223" s="8" t="inlineStr">
+        <is>
+          <t>SUHAI</t>
+        </is>
+      </c>
+      <c r="D223" s="8" t="inlineStr">
+        <is>
+          <t>TUCSON</t>
+        </is>
+      </c>
+      <c r="E223" s="9" t="n">
+        <v>25</v>
+      </c>
+      <c r="F223" s="10" t="n">
+        <v>422.46</v>
+      </c>
+      <c r="G223" s="10" t="n">
+        <v>109.84</v>
+      </c>
+      <c r="H223" s="10" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="I223" s="10" t="n">
+        <v>107.64</v>
+      </c>
+      <c r="J223" s="8" t="n">
+        <v>12</v>
+      </c>
+      <c r="K223" s="10" t="n">
+        <v>8.970000000000001</v>
+      </c>
+      <c r="L223" s="23" t="n">
+        <v>10</v>
+      </c>
+      <c r="M223" s="8" t="inlineStr">
+        <is>
+          <t>DE</t>
+        </is>
+      </c>
+      <c r="N223" s="12" t="n">
+        <v>12</v>
+      </c>
+      <c r="O223" s="10" t="n"/>
+      <c r="P223" s="13" t="inlineStr">
+        <is>
+          <t>Ativo</t>
+        </is>
+      </c>
+      <c r="Q223" s="13" t="inlineStr">
+        <is>
+          <t>Adimplente</t>
+        </is>
+      </c>
+      <c r="R223" s="14" t="inlineStr"/>
+    </row>
+    <row r="224" ht="16" customHeight="1">
+      <c r="A224" s="15" t="inlineStr">
+        <is>
+          <t>VALDISLEI XAVIER DO NASCIMENTO</t>
+        </is>
+      </c>
+      <c r="B224" s="16" t="n">
+        <v>4204.31</v>
+      </c>
+      <c r="C224" s="17" t="inlineStr">
+        <is>
+          <t>BRADESCO</t>
+        </is>
+      </c>
+      <c r="D224" s="17" t="inlineStr">
+        <is>
+          <t>COROLLA</t>
+        </is>
+      </c>
+      <c r="E224" s="18" t="n">
+        <v>20</v>
+      </c>
+      <c r="F224" s="19" t="n">
+        <v>840.86</v>
+      </c>
+      <c r="G224" s="19" t="n">
+        <v>218.62</v>
+      </c>
+      <c r="H224" s="19" t="n">
+        <v>4.37</v>
+      </c>
+      <c r="I224" s="19" t="n">
+        <v>214.25</v>
+      </c>
+      <c r="J224" s="17" t="n">
+        <v>10</v>
+      </c>
+      <c r="K224" s="19" t="n">
+        <v>21.43</v>
+      </c>
+      <c r="L224" s="24" t="n">
+        <v>9</v>
+      </c>
+      <c r="M224" s="17" t="inlineStr">
+        <is>
+          <t>DE</t>
+        </is>
+      </c>
+      <c r="N224" s="21" t="n">
+        <v>10</v>
+      </c>
+      <c r="O224" s="19" t="n"/>
+      <c r="P224" s="13" t="inlineStr">
+        <is>
+          <t>Ativo</t>
+        </is>
+      </c>
+      <c r="Q224" s="13" t="inlineStr">
+        <is>
+          <t>Adimplente</t>
+        </is>
+      </c>
+      <c r="R224" s="22" t="inlineStr"/>
+    </row>
+    <row r="225" ht="16" customHeight="1">
+      <c r="A225" s="6" t="inlineStr">
+        <is>
+          <t>IVO REIS DO NASCIMENTO</t>
+        </is>
+      </c>
+      <c r="B225" s="7" t="n">
+        <v>1199.51</v>
+      </c>
+      <c r="C225" s="8" t="inlineStr">
+        <is>
+          <t>AZUL</t>
+        </is>
+      </c>
+      <c r="D225" s="8" t="inlineStr">
+        <is>
+          <t>CITY SEDAN</t>
+        </is>
+      </c>
+      <c r="E225" s="9" t="n">
+        <v>20</v>
+      </c>
+      <c r="F225" s="10" t="n">
+        <v>239.9</v>
+      </c>
+      <c r="G225" s="10" t="n">
+        <v>62.37</v>
+      </c>
+      <c r="H225" s="10" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="I225" s="10" t="n">
+        <v>61.13</v>
+      </c>
+      <c r="J225" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="K225" s="10" t="n">
+        <v>61.13</v>
+      </c>
+      <c r="L225" s="23" t="n">
+        <v>9</v>
+      </c>
+      <c r="M225" s="8" t="inlineStr">
+        <is>
+          <t>DE</t>
+        </is>
+      </c>
+      <c r="N225" s="12" t="n">
+        <v>1</v>
+      </c>
+      <c r="O225" s="10" t="n"/>
+      <c r="P225" s="13" t="inlineStr">
+        <is>
+          <t>Ativo</t>
+        </is>
+      </c>
+      <c r="Q225" s="13" t="inlineStr">
+        <is>
+          <t>Adimplente</t>
+        </is>
+      </c>
+      <c r="R225" s="14" t="inlineStr"/>
+    </row>
+    <row r="226" ht="16" customHeight="1">
+      <c r="A226" s="15" t="inlineStr">
+        <is>
+          <t>ANDREA NASCIMENTO SANTANA MARTIENA</t>
+        </is>
+      </c>
+      <c r="B226" s="16" t="n">
+        <v>1986.95</v>
+      </c>
+      <c r="C226" s="17" t="inlineStr">
+        <is>
+          <t>TOKIO MARINE</t>
+        </is>
+      </c>
+      <c r="D226" s="17" t="inlineStr">
+        <is>
+          <t>CRETA</t>
+        </is>
+      </c>
+      <c r="E226" s="18" t="n">
+        <v>20</v>
+      </c>
+      <c r="F226" s="19" t="n">
+        <v>397.39</v>
+      </c>
+      <c r="G226" s="19" t="n">
+        <v>103.32</v>
+      </c>
+      <c r="H226" s="19" t="n">
+        <v>2.07</v>
+      </c>
+      <c r="I226" s="19" t="n">
+        <v>101.25</v>
+      </c>
+      <c r="J226" s="17" t="n">
+        <v>12</v>
+      </c>
+      <c r="K226" s="19" t="n">
+        <v>8.44</v>
+      </c>
+      <c r="L226" s="24" t="n">
+        <v>9</v>
+      </c>
+      <c r="M226" s="17" t="inlineStr">
+        <is>
+          <t>DE</t>
+        </is>
+      </c>
+      <c r="N226" s="21" t="n">
+        <v>12</v>
+      </c>
+      <c r="O226" s="19" t="n"/>
+      <c r="P226" s="13" t="inlineStr">
+        <is>
+          <t>Ativo</t>
+        </is>
+      </c>
+      <c r="Q226" s="13" t="inlineStr">
+        <is>
+          <t>Adimplente</t>
+        </is>
+      </c>
+      <c r="R226" s="22" t="inlineStr"/>
+    </row>
+    <row r="227" ht="16" customHeight="1">
+      <c r="A227" s="6" t="inlineStr">
+        <is>
+          <t>CAIO CESAR DOS SANTOS</t>
+        </is>
+      </c>
+      <c r="B227" s="7" t="n">
+        <v>3310.55</v>
+      </c>
+      <c r="C227" s="8" t="inlineStr">
+        <is>
+          <t>SUHAI</t>
+        </is>
+      </c>
+      <c r="D227" s="8" t="inlineStr">
+        <is>
+          <t>SIENA</t>
+        </is>
+      </c>
+      <c r="E227" s="9" t="n">
+        <v>20</v>
+      </c>
+      <c r="F227" s="10" t="n">
+        <v>662.11</v>
+      </c>
+      <c r="G227" s="10" t="n">
+        <v>172.15</v>
+      </c>
+      <c r="H227" s="10" t="n">
+        <v>3.44</v>
+      </c>
+      <c r="I227" s="10" t="n">
+        <v>168.71</v>
+      </c>
+      <c r="J227" s="8" t="n">
+        <v>12</v>
+      </c>
+      <c r="K227" s="10" t="n">
+        <v>14.06</v>
+      </c>
+      <c r="L227" s="23" t="n">
+        <v>8</v>
+      </c>
+      <c r="M227" s="8" t="inlineStr">
+        <is>
+          <t>DE</t>
+        </is>
+      </c>
+      <c r="N227" s="12" t="n">
+        <v>12</v>
+      </c>
+      <c r="O227" s="10" t="n"/>
+      <c r="P227" s="13" t="inlineStr">
+        <is>
+          <t>Ativo</t>
+        </is>
+      </c>
+      <c r="Q227" s="13" t="inlineStr">
+        <is>
+          <t>Adimplente</t>
+        </is>
+      </c>
+      <c r="R227" s="14" t="inlineStr"/>
+    </row>
+    <row r="228" ht="16" customHeight="1">
+      <c r="A228" s="15" t="inlineStr">
+        <is>
+          <t>IVO REIS DO NASCIMENTO</t>
+        </is>
+      </c>
+      <c r="B228" s="16" t="n">
+        <v>2141.74</v>
+      </c>
+      <c r="C228" s="17" t="inlineStr">
+        <is>
+          <t>MITSUI</t>
+        </is>
+      </c>
+      <c r="D228" s="17" t="inlineStr">
+        <is>
+          <t>FOX</t>
+        </is>
+      </c>
+      <c r="E228" s="18" t="n">
+        <v>20</v>
+      </c>
+      <c r="F228" s="19" t="n">
+        <v>428.35</v>
+      </c>
+      <c r="G228" s="19" t="n">
+        <v>111.37</v>
+      </c>
+      <c r="H228" s="19" t="n">
+        <v>2.23</v>
+      </c>
+      <c r="I228" s="19" t="n">
+        <v>109.14</v>
+      </c>
+      <c r="J228" s="17" t="n">
+        <v>10</v>
+      </c>
+      <c r="K228" s="19" t="n">
+        <v>10.91</v>
+      </c>
+      <c r="L228" s="24" t="n">
+        <v>8</v>
+      </c>
+      <c r="M228" s="17" t="inlineStr">
+        <is>
+          <t>DE</t>
+        </is>
+      </c>
+      <c r="N228" s="21" t="n">
+        <v>10</v>
+      </c>
+      <c r="O228" s="19" t="n"/>
+      <c r="P228" s="13" t="inlineStr">
+        <is>
+          <t>Ativo</t>
+        </is>
+      </c>
+      <c r="Q228" s="13" t="inlineStr">
+        <is>
+          <t>Adimplente</t>
+        </is>
+      </c>
+      <c r="R228" s="22" t="inlineStr"/>
+    </row>
+    <row r="229" ht="16" customHeight="1">
+      <c r="A229" s="6" t="inlineStr">
+        <is>
+          <t>LEIDE DAYANE DE SOUZA</t>
+        </is>
+      </c>
+      <c r="B229" s="7" t="n">
+        <v>1642.98</v>
+      </c>
+      <c r="C229" s="8" t="inlineStr">
+        <is>
+          <t>ALIRO</t>
+        </is>
+      </c>
+      <c r="D229" s="8" t="inlineStr">
+        <is>
+          <t>ECOSPORT</t>
+        </is>
+      </c>
+      <c r="E229" s="9" t="n">
+        <v>20</v>
+      </c>
+      <c r="F229" s="10" t="n">
+        <v>328.6</v>
+      </c>
+      <c r="G229" s="10" t="n">
+        <v>85.43000000000001</v>
+      </c>
+      <c r="H229" s="10" t="n">
+        <v>1.71</v>
+      </c>
+      <c r="I229" s="10" t="n">
+        <v>83.73</v>
+      </c>
+      <c r="J229" s="8" t="n">
+        <v>10</v>
+      </c>
+      <c r="K229" s="10" t="n">
+        <v>8.369999999999999</v>
+      </c>
+      <c r="L229" s="23" t="n">
+        <v>8</v>
+      </c>
+      <c r="M229" s="8" t="inlineStr">
+        <is>
+          <t>DE</t>
+        </is>
+      </c>
+      <c r="N229" s="12" t="n">
+        <v>10</v>
+      </c>
+      <c r="O229" s="10" t="n"/>
+      <c r="P229" s="13" t="inlineStr">
+        <is>
+          <t>Ativo</t>
+        </is>
+      </c>
+      <c r="Q229" s="13" t="inlineStr">
+        <is>
+          <t>Adimplente</t>
+        </is>
+      </c>
+      <c r="R229" s="14" t="inlineStr"/>
+    </row>
+    <row r="230" ht="18" customHeight="1">
+      <c r="A230" s="25" t="inlineStr">
+        <is>
+          <t>TOTAL  MAR/26</t>
+        </is>
+      </c>
+      <c r="K230" s="26" t="n">
+        <v>251.38</v>
+      </c>
+      <c r="L230" s="27" t="n"/>
+      <c r="M230" s="27" t="n"/>
+      <c r="N230" s="27" t="n"/>
+      <c r="O230" s="27" t="n"/>
+      <c r="P230" s="27" t="n"/>
+      <c r="Q230" s="27" t="n"/>
+      <c r="R230" s="27" t="n"/>
+    </row>
+    <row r="232" ht="22" customHeight="1">
+      <c r="A232" s="3" t="inlineStr">
         <is>
           <t>abr/26</t>
         </is>
       </c>
-      <c r="B148" s="4" t="inlineStr">
+      <c r="B232" s="4" t="inlineStr">
         <is>
           <t>PRÊMIO LÍQ</t>
         </is>
       </c>
-      <c r="C148" s="4" t="inlineStr">
+      <c r="C232" s="4" t="inlineStr">
         <is>
           <t>SEGURADORA</t>
         </is>
       </c>
-      <c r="D148" s="4" t="inlineStr">
+      <c r="D232" s="4" t="inlineStr">
         <is>
           <t>ITEM</t>
         </is>
       </c>
-      <c r="E148" s="4" t="inlineStr">
+      <c r="E232" s="4" t="inlineStr">
         <is>
           <t>COM%</t>
         </is>
       </c>
-      <c r="F148" s="4" t="inlineStr">
+      <c r="F232" s="4" t="inlineStr">
         <is>
           <t>COMISSÃO</t>
         </is>
       </c>
-      <c r="G148" s="4" t="inlineStr">
+      <c r="G232" s="4" t="inlineStr">
         <is>
           <t>26%</t>
         </is>
       </c>
-      <c r="H148" s="4" t="inlineStr">
+      <c r="H232" s="4" t="inlineStr">
         <is>
           <t>2% DA</t>
         </is>
       </c>
-      <c r="I148" s="4" t="inlineStr">
+      <c r="I232" s="4" t="inlineStr">
         <is>
           <t>RECEBIDO</t>
         </is>
       </c>
-      <c r="J148" s="4" t="inlineStr">
+      <c r="J232" s="4" t="inlineStr">
         <is>
           <t>VEZES</t>
         </is>
       </c>
-      <c r="K148" s="4" t="inlineStr">
+      <c r="K232" s="4" t="inlineStr">
         <is>
           <t>RECEBER</t>
         </is>
       </c>
-      <c r="L148" s="5" t="inlineStr"/>
-      <c r="M148" s="4" t="inlineStr">
-        <is>
-          <t>DE</t>
-        </is>
-      </c>
-      <c r="N148" s="5" t="inlineStr"/>
-      <c r="O148" s="4" t="inlineStr">
+      <c r="L232" s="5" t="inlineStr"/>
+      <c r="M232" s="4" t="inlineStr">
+        <is>
+          <t>DE</t>
+        </is>
+      </c>
+      <c r="N232" s="5" t="inlineStr"/>
+      <c r="O232" s="4" t="inlineStr">
         <is>
           <t>AJUSTE</t>
         </is>
       </c>
-      <c r="P148" s="4" t="inlineStr">
+      <c r="P232" s="4" t="inlineStr">
         <is>
           <t>STATUS</t>
         </is>
       </c>
-      <c r="Q148" s="4" t="inlineStr">
+      <c r="Q232" s="4" t="inlineStr">
         <is>
           <t>ADIMPLÊNCIA</t>
         </is>
       </c>
-      <c r="R148" s="4" t="inlineStr">
+      <c r="R232" s="4" t="inlineStr">
         <is>
           <t>OBS</t>
         </is>
       </c>
     </row>
-    <row r="149" ht="16" customHeight="1">
-      <c r="A149" s="28" t="inlineStr">
-        <is>
-          <t>⚠  Dados de abr/26 ainda não inseridos — preencher manualmente</t>
-        </is>
-      </c>
+    <row r="233" ht="16" customHeight="1">
+      <c r="A233" s="6" t="inlineStr">
+        <is>
+          <t>ROSANGELA DE JESUS MELO</t>
+        </is>
+      </c>
+      <c r="B233" s="7" t="n">
+        <v>1454.42</v>
+      </c>
+      <c r="C233" s="8" t="inlineStr">
+        <is>
+          <t>SUHAI</t>
+        </is>
+      </c>
+      <c r="D233" s="8" t="inlineStr">
+        <is>
+          <t>IDEA</t>
+        </is>
+      </c>
+      <c r="E233" s="9" t="n">
+        <v>25</v>
+      </c>
+      <c r="F233" s="10" t="n">
+        <v>363.61</v>
+      </c>
+      <c r="G233" s="10" t="n">
+        <v>94.54000000000001</v>
+      </c>
+      <c r="H233" s="10" t="n">
+        <v>1.89</v>
+      </c>
+      <c r="I233" s="10" t="n">
+        <v>92.65000000000001</v>
+      </c>
+      <c r="J233" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="K233" s="10" t="n">
+        <v>92.65000000000001</v>
+      </c>
+      <c r="L233" s="23" t="n">
+        <v>11</v>
+      </c>
+      <c r="M233" s="8" t="inlineStr">
+        <is>
+          <t>DE</t>
+        </is>
+      </c>
+      <c r="N233" s="12" t="n">
+        <v>1</v>
+      </c>
+      <c r="O233" s="10" t="n"/>
+      <c r="P233" s="13" t="inlineStr">
+        <is>
+          <t>Ativo</t>
+        </is>
+      </c>
+      <c r="Q233" s="13" t="inlineStr">
+        <is>
+          <t>Adimplente</t>
+        </is>
+      </c>
+      <c r="R233" s="14" t="inlineStr"/>
+    </row>
+    <row r="234" ht="16" customHeight="1">
+      <c r="A234" s="15" t="inlineStr">
+        <is>
+          <t>LEONARDO VAZ DE FREITAS</t>
+        </is>
+      </c>
+      <c r="B234" s="16" t="n">
+        <v>1689.84</v>
+      </c>
+      <c r="C234" s="17" t="inlineStr">
+        <is>
+          <t>SUHAI</t>
+        </is>
+      </c>
+      <c r="D234" s="17" t="inlineStr">
+        <is>
+          <t>TUCSON</t>
+        </is>
+      </c>
+      <c r="E234" s="18" t="n">
+        <v>25</v>
+      </c>
+      <c r="F234" s="19" t="n">
+        <v>422.46</v>
+      </c>
+      <c r="G234" s="19" t="n">
+        <v>109.84</v>
+      </c>
+      <c r="H234" s="19" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="I234" s="19" t="n">
+        <v>107.64</v>
+      </c>
+      <c r="J234" s="17" t="n">
+        <v>12</v>
+      </c>
+      <c r="K234" s="19" t="n">
+        <v>8.970000000000001</v>
+      </c>
+      <c r="L234" s="24" t="n">
+        <v>11</v>
+      </c>
+      <c r="M234" s="17" t="inlineStr">
+        <is>
+          <t>DE</t>
+        </is>
+      </c>
+      <c r="N234" s="21" t="n">
+        <v>12</v>
+      </c>
+      <c r="O234" s="19" t="n"/>
+      <c r="P234" s="13" t="inlineStr">
+        <is>
+          <t>Ativo</t>
+        </is>
+      </c>
+      <c r="Q234" s="13" t="inlineStr">
+        <is>
+          <t>Adimplente</t>
+        </is>
+      </c>
+      <c r="R234" s="22" t="inlineStr"/>
+    </row>
+    <row r="235" ht="16" customHeight="1">
+      <c r="A235" s="6" t="inlineStr">
+        <is>
+          <t>VALDISLEI XAVIER DO NASCIMENTO</t>
+        </is>
+      </c>
+      <c r="B235" s="7" t="n">
+        <v>4204.31</v>
+      </c>
+      <c r="C235" s="8" t="inlineStr">
+        <is>
+          <t>BRADESCO</t>
+        </is>
+      </c>
+      <c r="D235" s="8" t="inlineStr">
+        <is>
+          <t>COROLLA</t>
+        </is>
+      </c>
+      <c r="E235" s="9" t="n">
+        <v>20</v>
+      </c>
+      <c r="F235" s="10" t="n">
+        <v>840.86</v>
+      </c>
+      <c r="G235" s="10" t="n">
+        <v>218.62</v>
+      </c>
+      <c r="H235" s="10" t="n">
+        <v>4.37</v>
+      </c>
+      <c r="I235" s="10" t="n">
+        <v>214.25</v>
+      </c>
+      <c r="J235" s="8" t="n">
+        <v>10</v>
+      </c>
+      <c r="K235" s="10" t="n">
+        <v>21.43</v>
+      </c>
+      <c r="L235" s="11" t="n">
+        <v>10</v>
+      </c>
+      <c r="M235" s="8" t="inlineStr">
+        <is>
+          <t>DE</t>
+        </is>
+      </c>
+      <c r="N235" s="12" t="n">
+        <v>10</v>
+      </c>
+      <c r="O235" s="10" t="n"/>
+      <c r="P235" s="13" t="inlineStr">
+        <is>
+          <t>Ativo</t>
+        </is>
+      </c>
+      <c r="Q235" s="13" t="inlineStr">
+        <is>
+          <t>Adimplente</t>
+        </is>
+      </c>
+      <c r="R235" s="14" t="inlineStr"/>
+    </row>
+    <row r="236" ht="16" customHeight="1">
+      <c r="A236" s="15" t="inlineStr">
+        <is>
+          <t>IVO REIS DO NASCIMENTO</t>
+        </is>
+      </c>
+      <c r="B236" s="16" t="n">
+        <v>1199.51</v>
+      </c>
+      <c r="C236" s="17" t="inlineStr">
+        <is>
+          <t>AZUL</t>
+        </is>
+      </c>
+      <c r="D236" s="17" t="inlineStr">
+        <is>
+          <t>CITY SEDAN</t>
+        </is>
+      </c>
+      <c r="E236" s="18" t="n">
+        <v>20</v>
+      </c>
+      <c r="F236" s="19" t="n">
+        <v>239.9</v>
+      </c>
+      <c r="G236" s="19" t="n">
+        <v>62.37</v>
+      </c>
+      <c r="H236" s="19" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="I236" s="19" t="n">
+        <v>61.13</v>
+      </c>
+      <c r="J236" s="17" t="n">
+        <v>1</v>
+      </c>
+      <c r="K236" s="19" t="n">
+        <v>61.13</v>
+      </c>
+      <c r="L236" s="24" t="n">
+        <v>10</v>
+      </c>
+      <c r="M236" s="17" t="inlineStr">
+        <is>
+          <t>DE</t>
+        </is>
+      </c>
+      <c r="N236" s="21" t="n">
+        <v>1</v>
+      </c>
+      <c r="O236" s="19" t="n"/>
+      <c r="P236" s="13" t="inlineStr">
+        <is>
+          <t>Ativo</t>
+        </is>
+      </c>
+      <c r="Q236" s="13" t="inlineStr">
+        <is>
+          <t>Adimplente</t>
+        </is>
+      </c>
+      <c r="R236" s="22" t="inlineStr"/>
+    </row>
+    <row r="237" ht="16" customHeight="1">
+      <c r="A237" s="6" t="inlineStr">
+        <is>
+          <t>ANDREA NASCIMENTO SANTANA MARTIENA</t>
+        </is>
+      </c>
+      <c r="B237" s="7" t="n">
+        <v>1986.95</v>
+      </c>
+      <c r="C237" s="8" t="inlineStr">
+        <is>
+          <t>TOKIO MARINE</t>
+        </is>
+      </c>
+      <c r="D237" s="8" t="inlineStr">
+        <is>
+          <t>CRETA</t>
+        </is>
+      </c>
+      <c r="E237" s="9" t="n">
+        <v>20</v>
+      </c>
+      <c r="F237" s="10" t="n">
+        <v>397.39</v>
+      </c>
+      <c r="G237" s="10" t="n">
+        <v>103.32</v>
+      </c>
+      <c r="H237" s="10" t="n">
+        <v>2.07</v>
+      </c>
+      <c r="I237" s="10" t="n">
+        <v>101.25</v>
+      </c>
+      <c r="J237" s="8" t="n">
+        <v>12</v>
+      </c>
+      <c r="K237" s="10" t="n">
+        <v>8.44</v>
+      </c>
+      <c r="L237" s="23" t="n">
+        <v>10</v>
+      </c>
+      <c r="M237" s="8" t="inlineStr">
+        <is>
+          <t>DE</t>
+        </is>
+      </c>
+      <c r="N237" s="12" t="n">
+        <v>12</v>
+      </c>
+      <c r="O237" s="10" t="n"/>
+      <c r="P237" s="13" t="inlineStr">
+        <is>
+          <t>Ativo</t>
+        </is>
+      </c>
+      <c r="Q237" s="13" t="inlineStr">
+        <is>
+          <t>Adimplente</t>
+        </is>
+      </c>
+      <c r="R237" s="14" t="inlineStr"/>
+    </row>
+    <row r="238" ht="16" customHeight="1">
+      <c r="A238" s="15" t="inlineStr">
+        <is>
+          <t>CAIO CESAR DOS SANTOS</t>
+        </is>
+      </c>
+      <c r="B238" s="16" t="n">
+        <v>3310.55</v>
+      </c>
+      <c r="C238" s="17" t="inlineStr">
+        <is>
+          <t>SUHAI</t>
+        </is>
+      </c>
+      <c r="D238" s="17" t="inlineStr">
+        <is>
+          <t>SIENA</t>
+        </is>
+      </c>
+      <c r="E238" s="18" t="n">
+        <v>20</v>
+      </c>
+      <c r="F238" s="19" t="n">
+        <v>662.11</v>
+      </c>
+      <c r="G238" s="19" t="n">
+        <v>172.15</v>
+      </c>
+      <c r="H238" s="19" t="n">
+        <v>3.44</v>
+      </c>
+      <c r="I238" s="19" t="n">
+        <v>168.71</v>
+      </c>
+      <c r="J238" s="17" t="n">
+        <v>12</v>
+      </c>
+      <c r="K238" s="19" t="n">
+        <v>14.06</v>
+      </c>
+      <c r="L238" s="24" t="n">
+        <v>9</v>
+      </c>
+      <c r="M238" s="17" t="inlineStr">
+        <is>
+          <t>DE</t>
+        </is>
+      </c>
+      <c r="N238" s="21" t="n">
+        <v>12</v>
+      </c>
+      <c r="O238" s="19" t="n"/>
+      <c r="P238" s="13" t="inlineStr">
+        <is>
+          <t>Ativo</t>
+        </is>
+      </c>
+      <c r="Q238" s="13" t="inlineStr">
+        <is>
+          <t>Adimplente</t>
+        </is>
+      </c>
+      <c r="R238" s="22" t="inlineStr"/>
+    </row>
+    <row r="239" ht="16" customHeight="1">
+      <c r="A239" s="6" t="inlineStr">
+        <is>
+          <t>IVO REIS DO NASCIMENTO</t>
+        </is>
+      </c>
+      <c r="B239" s="7" t="n">
+        <v>2141.74</v>
+      </c>
+      <c r="C239" s="8" t="inlineStr">
+        <is>
+          <t>MITSUI</t>
+        </is>
+      </c>
+      <c r="D239" s="8" t="inlineStr">
+        <is>
+          <t>FOX</t>
+        </is>
+      </c>
+      <c r="E239" s="9" t="n">
+        <v>20</v>
+      </c>
+      <c r="F239" s="10" t="n">
+        <v>428.35</v>
+      </c>
+      <c r="G239" s="10" t="n">
+        <v>111.37</v>
+      </c>
+      <c r="H239" s="10" t="n">
+        <v>2.23</v>
+      </c>
+      <c r="I239" s="10" t="n">
+        <v>109.14</v>
+      </c>
+      <c r="J239" s="8" t="n">
+        <v>10</v>
+      </c>
+      <c r="K239" s="10" t="n">
+        <v>10.91</v>
+      </c>
+      <c r="L239" s="23" t="n">
+        <v>9</v>
+      </c>
+      <c r="M239" s="8" t="inlineStr">
+        <is>
+          <t>DE</t>
+        </is>
+      </c>
+      <c r="N239" s="12" t="n">
+        <v>10</v>
+      </c>
+      <c r="O239" s="10" t="n"/>
+      <c r="P239" s="13" t="inlineStr">
+        <is>
+          <t>Ativo</t>
+        </is>
+      </c>
+      <c r="Q239" s="13" t="inlineStr">
+        <is>
+          <t>Adimplente</t>
+        </is>
+      </c>
+      <c r="R239" s="14" t="inlineStr"/>
+    </row>
+    <row r="240" ht="16" customHeight="1">
+      <c r="A240" s="15" t="inlineStr">
+        <is>
+          <t>LEIDE DAYANE DE SOUZA</t>
+        </is>
+      </c>
+      <c r="B240" s="16" t="n">
+        <v>1642.98</v>
+      </c>
+      <c r="C240" s="17" t="inlineStr">
+        <is>
+          <t>ALIRO</t>
+        </is>
+      </c>
+      <c r="D240" s="17" t="inlineStr">
+        <is>
+          <t>ECOSPORT</t>
+        </is>
+      </c>
+      <c r="E240" s="18" t="n">
+        <v>20</v>
+      </c>
+      <c r="F240" s="19" t="n">
+        <v>328.6</v>
+      </c>
+      <c r="G240" s="19" t="n">
+        <v>85.43000000000001</v>
+      </c>
+      <c r="H240" s="19" t="n">
+        <v>1.71</v>
+      </c>
+      <c r="I240" s="19" t="n">
+        <v>83.73</v>
+      </c>
+      <c r="J240" s="17" t="n">
+        <v>10</v>
+      </c>
+      <c r="K240" s="19" t="n">
+        <v>8.369999999999999</v>
+      </c>
+      <c r="L240" s="24" t="n">
+        <v>9</v>
+      </c>
+      <c r="M240" s="17" t="inlineStr">
+        <is>
+          <t>DE</t>
+        </is>
+      </c>
+      <c r="N240" s="21" t="n">
+        <v>10</v>
+      </c>
+      <c r="O240" s="19" t="n"/>
+      <c r="P240" s="13" t="inlineStr">
+        <is>
+          <t>Ativo</t>
+        </is>
+      </c>
+      <c r="Q240" s="13" t="inlineStr">
+        <is>
+          <t>Adimplente</t>
+        </is>
+      </c>
+      <c r="R240" s="22" t="inlineStr"/>
+    </row>
+    <row r="241" ht="18" customHeight="1">
+      <c r="A241" s="25" t="inlineStr">
+        <is>
+          <t>TOTAL  ABR/26</t>
+        </is>
+      </c>
+      <c r="K241" s="26" t="n">
+        <v>225.96</v>
+      </c>
+      <c r="L241" s="27" t="n"/>
+      <c r="M241" s="27" t="n"/>
+      <c r="N241" s="27" t="n"/>
+      <c r="O241" s="27" t="n"/>
+      <c r="P241" s="27" t="n"/>
+      <c r="Q241" s="27" t="n"/>
+      <c r="R241" s="27" t="n"/>
     </row>
   </sheetData>
   <mergeCells count="15">
     <mergeCell ref="A26:R26"/>
-    <mergeCell ref="A140:R140"/>
+    <mergeCell ref="A216:J216"/>
     <mergeCell ref="A23:J23"/>
-    <mergeCell ref="A143:R143"/>
-    <mergeCell ref="A134:R134"/>
+    <mergeCell ref="A230:J230"/>
+    <mergeCell ref="A241:J241"/>
+    <mergeCell ref="A202:J202"/>
     <mergeCell ref="A2:R2"/>
-    <mergeCell ref="A137:R137"/>
+    <mergeCell ref="A150:J150"/>
     <mergeCell ref="A78:J78"/>
     <mergeCell ref="A1:R1"/>
-    <mergeCell ref="A146:R146"/>
+    <mergeCell ref="A171:J171"/>
+    <mergeCell ref="A187:J187"/>
     <mergeCell ref="A104:J104"/>
-    <mergeCell ref="A149:R149"/>
     <mergeCell ref="A128:J128"/>
-    <mergeCell ref="A131:R131"/>
     <mergeCell ref="A51:J51"/>
   </mergeCells>
-  <conditionalFormatting sqref="A4:R127">
+  <conditionalFormatting sqref="A4:R240">
     <cfRule type="expression" priority="1" dxfId="0">
       <formula>$P4="Inativo"</formula>
     </cfRule>
@@ -8976,10 +14928,10 @@
     </cfRule>
   </conditionalFormatting>
   <dataValidations count="2">
-    <dataValidation sqref="P4:P127" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="0" errorTitle="Inválido" error="Escolha: Ativo ou Inativo" type="list">
+    <dataValidation sqref="P4:P240" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="0" errorTitle="Inválido" error="Escolha: Ativo ou Inativo" type="list">
       <formula1>"Ativo,Inativo"</formula1>
     </dataValidation>
-    <dataValidation sqref="Q4:Q127" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="0" errorTitle="Inválido" error="Escolha: Adimplente ou Inadimplente" type="list">
+    <dataValidation sqref="Q4:Q240" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="0" errorTitle="Inválido" error="Escolha: Adimplente ou Inadimplente" type="list">
       <formula1>"Adimplente,Inadimplente"</formula1>
     </dataValidation>
   </dataValidations>
@@ -9201,17 +15153,21 @@
           <t>out/25</t>
         </is>
       </c>
-      <c r="B9" s="31" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="C9" s="37" t="n"/>
-      <c r="D9" s="37" t="n"/>
-      <c r="E9" s="37" t="n"/>
-      <c r="F9" s="38" t="inlineStr">
-        <is>
-          <t>⚠ Aguardando dados</t>
+      <c r="B9" s="31" t="n">
+        <v>19</v>
+      </c>
+      <c r="C9" s="32" t="n">
+        <v>38319.98</v>
+      </c>
+      <c r="D9" s="32" t="n">
+        <v>7573.620000000001</v>
+      </c>
+      <c r="E9" s="32" t="n">
+        <v>114</v>
+      </c>
+      <c r="F9" s="31" t="inlineStr">
+        <is>
+          <t>✅ Dados OK</t>
         </is>
       </c>
       <c r="G9" s="31" t="inlineStr"/>
@@ -9222,17 +15178,21 @@
           <t>nov/25</t>
         </is>
       </c>
-      <c r="B10" s="33" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="C10" s="34" t="n"/>
-      <c r="D10" s="34" t="n"/>
-      <c r="E10" s="34" t="n"/>
-      <c r="F10" s="35" t="inlineStr">
-        <is>
-          <t>⚠ Aguardando dados</t>
+      <c r="B10" s="33" t="n">
+        <v>18</v>
+      </c>
+      <c r="C10" s="36" t="n">
+        <v>37993.02</v>
+      </c>
+      <c r="D10" s="36" t="n">
+        <v>7508.23</v>
+      </c>
+      <c r="E10" s="36" t="n">
+        <v>129</v>
+      </c>
+      <c r="F10" s="33" t="inlineStr">
+        <is>
+          <t>✅ Dados OK</t>
         </is>
       </c>
       <c r="G10" s="33" t="inlineStr"/>
@@ -9243,17 +15203,21 @@
           <t>dez/25</t>
         </is>
       </c>
-      <c r="B11" s="31" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="C11" s="37" t="n"/>
-      <c r="D11" s="37" t="n"/>
-      <c r="E11" s="37" t="n"/>
-      <c r="F11" s="38" t="inlineStr">
-        <is>
-          <t>⚠ Aguardando dados</t>
+      <c r="B11" s="31" t="n">
+        <v>13</v>
+      </c>
+      <c r="C11" s="32" t="n">
+        <v>27131.27</v>
+      </c>
+      <c r="D11" s="32" t="n">
+        <v>5502.360000000001</v>
+      </c>
+      <c r="E11" s="32" t="n">
+        <v>93</v>
+      </c>
+      <c r="F11" s="31" t="inlineStr">
+        <is>
+          <t>✅ Dados OK</t>
         </is>
       </c>
       <c r="G11" s="31" t="inlineStr"/>
@@ -9264,17 +15228,21 @@
           <t>jan/26</t>
         </is>
       </c>
-      <c r="B12" s="33" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="C12" s="34" t="n"/>
-      <c r="D12" s="34" t="n"/>
-      <c r="E12" s="34" t="n"/>
-      <c r="F12" s="35" t="inlineStr">
-        <is>
-          <t>⚠ Aguardando dados</t>
+      <c r="B12" s="33" t="n">
+        <v>12</v>
+      </c>
+      <c r="C12" s="36" t="n">
+        <v>25042.19</v>
+      </c>
+      <c r="D12" s="36" t="n">
+        <v>5084.540000000001</v>
+      </c>
+      <c r="E12" s="36" t="n">
+        <v>93</v>
+      </c>
+      <c r="F12" s="33" t="inlineStr">
+        <is>
+          <t>✅ Dados OK</t>
         </is>
       </c>
       <c r="G12" s="33" t="inlineStr"/>
@@ -9285,17 +15253,21 @@
           <t>fev/26</t>
         </is>
       </c>
-      <c r="B13" s="31" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="C13" s="37" t="n"/>
-      <c r="D13" s="37" t="n"/>
-      <c r="E13" s="37" t="n"/>
-      <c r="F13" s="38" t="inlineStr">
-        <is>
-          <t>⚠ Aguardando dados</t>
+      <c r="B13" s="31" t="n">
+        <v>11</v>
+      </c>
+      <c r="C13" s="32" t="n">
+        <v>23289.45</v>
+      </c>
+      <c r="D13" s="32" t="n">
+        <v>4733.990000000001</v>
+      </c>
+      <c r="E13" s="32" t="n">
+        <v>92</v>
+      </c>
+      <c r="F13" s="31" t="inlineStr">
+        <is>
+          <t>✅ Dados OK</t>
         </is>
       </c>
       <c r="G13" s="31" t="inlineStr"/>
@@ -9306,17 +15278,21 @@
           <t>mar/26</t>
         </is>
       </c>
-      <c r="B14" s="33" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="C14" s="34" t="n"/>
-      <c r="D14" s="34" t="n"/>
-      <c r="E14" s="34" t="n"/>
-      <c r="F14" s="35" t="inlineStr">
-        <is>
-          <t>⚠ Aguardando dados</t>
+      <c r="B14" s="33" t="n">
+        <v>11</v>
+      </c>
+      <c r="C14" s="36" t="n">
+        <v>23289.45</v>
+      </c>
+      <c r="D14" s="36" t="n">
+        <v>4733.990000000001</v>
+      </c>
+      <c r="E14" s="36" t="n">
+        <v>103</v>
+      </c>
+      <c r="F14" s="33" t="inlineStr">
+        <is>
+          <t>✅ Dados OK</t>
         </is>
       </c>
       <c r="G14" s="33" t="inlineStr"/>
@@ -9327,39 +15303,43 @@
           <t>abr/26</t>
         </is>
       </c>
-      <c r="B15" s="31" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="C15" s="37" t="n"/>
-      <c r="D15" s="37" t="n"/>
-      <c r="E15" s="37" t="n"/>
-      <c r="F15" s="38" t="inlineStr">
-        <is>
-          <t>⚠ Aguardando dados</t>
+      <c r="B15" s="31" t="n">
+        <v>8</v>
+      </c>
+      <c r="C15" s="32" t="n">
+        <v>17630.3</v>
+      </c>
+      <c r="D15" s="32" t="n">
+        <v>3683.28</v>
+      </c>
+      <c r="E15" s="32" t="n">
+        <v>79</v>
+      </c>
+      <c r="F15" s="31" t="inlineStr">
+        <is>
+          <t>✅ Dados OK</t>
         </is>
       </c>
       <c r="G15" s="31" t="inlineStr"/>
     </row>
     <row r="16" ht="22" customHeight="1">
-      <c r="A16" s="39" t="inlineStr">
+      <c r="A16" s="37" t="inlineStr">
         <is>
           <t>TOTAL</t>
         </is>
       </c>
-      <c r="B16" s="40" t="n"/>
-      <c r="C16" s="41" t="n">
-        <v>233848.81</v>
-      </c>
-      <c r="D16" s="41" t="n">
-        <v>44468.32999999999</v>
-      </c>
-      <c r="E16" s="41" t="n">
-        <v>511</v>
-      </c>
-      <c r="F16" s="40" t="n"/>
-      <c r="G16" s="40" t="n"/>
+      <c r="B16" s="38" t="n"/>
+      <c r="C16" s="39" t="n">
+        <v>426544.47</v>
+      </c>
+      <c r="D16" s="39" t="n">
+        <v>83288.34000000001</v>
+      </c>
+      <c r="E16" s="39" t="n">
+        <v>1214</v>
+      </c>
+      <c r="F16" s="38" t="n"/>
+      <c r="G16" s="38" t="n"/>
     </row>
   </sheetData>
   <mergeCells count="1">
